--- a/output/совпадения_после_отбрасывания_префикса.xlsx
+++ b/output/совпадения_после_отбрасывания_префикса.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E294"/>
+  <dimension ref="A1:E301"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -895,7 +895,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -904,17 +904,17 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>организации, получившие убыток от продаж: количество организаций (единиц)</t>
+          <t>организации, получившие убыток от продаж: убыточность в % к коммерческим и управленческим расходам</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>количество организаций единиц</t>
+          <t>коммерческим и управленческим расходам</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>OrgPolUbyOtProKolOrg(ed</t>
+          <t>OrgPolUbyOtProUbyV%KKomIUprRas</t>
         </is>
       </c>
     </row>
@@ -929,23 +929,23 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>организации, получившие убыток от продаж: в том числе: коммерческие и управленческие расходы</t>
+          <t>организации, получившие убыток от продаж: количество организаций (единиц)</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>том числе коммерческие и управленческие расходы</t>
+          <t>количество организаций единиц</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>OrgPolUbyOtProVToChiKomIUprRas</t>
+          <t>OrgPolUbyOtProKolOrg(ed</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -954,23 +954,23 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>организации, получившие убыток от продаж: количество организаций (единиц)</t>
+          <t>организации, получившие убыток от продаж: в том числе: коммерческие и управленческие расходы</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>количество организаций единиц</t>
+          <t>том числе коммерческие и управленческие расходы</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>OrgPolUbyOtProKolOrg(ed</t>
+          <t>OrgPolUbyOtProVToChiKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -979,23 +979,23 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>организации, получившие убыток от продаж: в том числе: коммерческие и управленческие расходы</t>
+          <t>организации, получившие убыток от продаж: убыточность в % к коммерческим и управленческим расходам</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>том числе коммерческие и управленческие расходы</t>
+          <t>коммерческим и управленческим расходам</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>OrgPolUbyOtProVToChiKomIUprRas</t>
+          <t>OrgPolUbyOtProUbyV%KKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -1054,23 +1054,23 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>организации, получившие убыток от продаж: количество организаций (единиц)</t>
+          <t>организации, получившие убыток от продаж: убыточность в % к коммерческим и управленческим расходам</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>количество организаций единиц</t>
+          <t>коммерческим и управленческим расходам</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>OrgPolUbyOtProKolOrg(ed</t>
+          <t>OrgPolUbyOtProUbyV%KKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -1079,23 +1079,23 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>организации, получившие убыток от продаж: в том числе: коммерческие и управленческие расходы</t>
+          <t>организации, получившие убыток от продаж: количество организаций (единиц)</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>том числе коммерческие и управленческие расходы</t>
+          <t>количество организаций единиц</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>OrgPolUbyOtProVToChiKomIUprRas</t>
+          <t>OrgPolUbyOtProKolOrg(ed</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -1104,23 +1104,23 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>организации, получившие убыток от продаж: количество организаций (единиц)</t>
+          <t>организации, получившие убыток от продаж: в том числе: коммерческие и управленческие расходы</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>количество организаций единиц</t>
+          <t>том числе коммерческие и управленческие расходы</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>OrgPolUbyOtProKolOrg(ed</t>
+          <t>OrgPolUbyOtProVToChiKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -1129,23 +1129,23 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>организации, получившие убыток от продаж: в том числе: коммерческие и управленческие расходы</t>
+          <t>организации, получившие убыток от продаж: убыточность в % к коммерческим и управленческим расходам</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>том числе коммерческие и управленческие расходы</t>
+          <t>коммерческим и управленческим расходам</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>OrgPolUbyOtProVToChiKomIUprRas</t>
+          <t>OrgPolUbyOtProUbyV%KKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -1170,7 +1170,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -1195,7 +1195,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -1204,7 +1204,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>уровень рентабельности, убыточности (-) в % к коммерческим и управленческим расходам</t>
+          <t>организации, получившие убыток от продаж: убыточность в % к коммерческим и управленческим расходам</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1214,13 +1214,13 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>UroRenUby(-V%KKomIUprRas</t>
+          <t>OrgPolUbyOtProUbyV%KKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -1229,23 +1229,23 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>уровень рентабельности, убыточности (-) в % к коммерческим и управленческим расходам</t>
+          <t>организации, получившие убыток от продаж: количество организаций (единиц)</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>коммерческим и управленческим расходам</t>
+          <t>количество организаций единиц</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>UroRenUby(-V%KKomIUprRas</t>
+          <t>OrgPolUbyOtProKolOrg(ed</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -1254,23 +1254,23 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>уровень рентабельности, убыточности (-) в % к коммерческим и управленческим расходам</t>
+          <t>организации, получившие убыток от продаж: в том числе: коммерческие и управленческие расходы</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>коммерческим и управленческим расходам</t>
+          <t>том числе коммерческие и управленческие расходы</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>UroRenUby(-V%KKomIUprRas</t>
+          <t>OrgPolUbyOtProVToChiKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>уровень рентабельности, убыточности (-) в % к коммерческим и управленческим расходам</t>
+          <t>организации, получившие убыток от продаж: убыточность в % к коммерческим и управленческим расходам</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1289,22 +1289,22 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>UroRenUby(-V%KKomIUprRas</t>
+          <t>OrgPolUbyOtProUbyV%KKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>T24_000000_t28Ved14.xlsx</t>
+          <t>T24_000000_t26Ved14.xlsx</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>коэффициент текущей ликвидности от &gt; = 100% до &lt; 200% количество организаций (единиц)</t>
+          <t>организации, получившие убыток от продаж: количество организаций (единиц)</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1314,157 +1314,157 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>KoeTekLikOt&gt;=10Do&lt;20KolOrg(ed</t>
+          <t>OrgPolUbyOtProKolOrg(ed</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>T24_000000_t28Ved14.xlsx</t>
+          <t>T24_000000_t26Ved14.xlsx</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>коэффициент текущей ликвидности от &gt; = 100% до &lt; 200% в % к общему количеству</t>
+          <t>организации, получившие убыток от продаж: в том числе: коммерческие и управленческие расходы</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>общему количеству</t>
+          <t>том числе коммерческие и управленческие расходы</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>KoeTekLikOt&gt;=10Do&lt;20V%KObsKol</t>
+          <t>OrgPolUbyOtProVToChiKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>T24_000000_t28Ved14.xlsx</t>
+          <t>T24_000000_t26Ved14.xlsx</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>коэффициент текущей ликвидности от &gt; = 100% до &lt; 200% дебиторская задолженность</t>
+          <t>организации, получившие убыток от продаж: убыточность в % к коммерческим и управленческим расходам</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>дебиторская задолженность</t>
+          <t>коммерческим и управленческим расходам</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>KoeTekLikOt&gt;=10Do&lt;20DebZad</t>
+          <t>OrgPolUbyOtProUbyV%KKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>T24_000000_t28Ved14.xlsx</t>
+          <t>T24_000000_t26Ved14.xlsx</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>коэффициент текущей ликвидности от &gt; = 100% до &lt; 200% в % к общей задолженности</t>
+          <t>уровень рентабельности, убыточности (-) в % к коммерческим и управленческим расходам</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>общей задолженности</t>
+          <t>коммерческим и управленческим расходам</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>KoeTekLikOt&gt;=10Do&lt;20V%KObsZad,KoeTekLikOt&gt;=10Do&lt;20V%KObsZadKre</t>
+          <t>UroRenUby(-V%KKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>T24_000000_t28Ved14.xlsx</t>
+          <t>T24_000000_t26Ved14.xlsx</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>коэффициент текущей ликвидности от &gt; = 100% до &lt; 200% кредиторская задолженность</t>
+          <t>уровень рентабельности, убыточности (-) в % к коммерческим и управленческим расходам</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>кредиторская задолженность</t>
+          <t>коммерческим и управленческим расходам</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>KoeTekLikOt&gt;=10Do&lt;20KreZad</t>
+          <t>UroRenUby(-V%KKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>T24_000000_t28Ved14.xlsx</t>
+          <t>T24_000000_t26Ved14.xlsx</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>коэффициент текущей ликвидности от &gt; = 100% до &lt; 200% денежные средства и денежные эквиваленты</t>
+          <t>уровень рентабельности, убыточности (-) в % к коммерческим и управленческим расходам</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>денежные средства и денежные эквиваленты</t>
+          <t>коммерческим и управленческим расходам</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>KoeTekLikOt&gt;=10Do&lt;20DenSreIDenEkv</t>
+          <t>UroRenUby(-V%KKomIUprRas</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>T24_000000_t28Ved14.xlsx</t>
+          <t>T24_000000_t26Ved14.xlsx</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>коэффициент текущей ликвидности от &gt; = 100% до &lt; 200% в % ко всем денежным средствам денежным эквивалентам</t>
+          <t>уровень рентабельности, убыточности (-) в % к коммерческим и управленческим расходам</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>в ко всем денежным средствам денежным эквивалентам</t>
+          <t>коммерческим и управленческим расходам</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>KoeTekLikOt&gt;=10Do&lt;20V%KoVsDenSreDenEkv</t>
+          <t>UroRenUby(-V%KKomIUprRas</t>
         </is>
       </c>
     </row>
@@ -1479,7 +1479,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>коэффициент текущей ликвидности от &gt; = 200% количество организаций (единиц)</t>
+          <t>коэффициент текущей ликвидности от &gt; = 100% до &lt; 200% количество организаций (единиц)</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1489,7 +1489,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>KoeTekLikOt&gt;=20KolOrg(ed</t>
+          <t>KoeTekLikOt&gt;=10Do&lt;20KolOrg(ed</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>коэффициент текущей ликвидности от &gt; = 200% в % к общему количеству</t>
+          <t>коэффициент текущей ликвидности от &gt; = 100% до &lt; 200% в % к общему количеству</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1514,7 +1514,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>KoeTekLikOt&gt;=20V%KObsKol</t>
+          <t>KoeTekLikOt&gt;=10Do&lt;20V%KObsKol</t>
         </is>
       </c>
     </row>
@@ -1529,7 +1529,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>коэффициент текущей ликвидности от &gt; = 200% дебиторская задолженность</t>
+          <t>коэффициент текущей ликвидности от &gt; = 100% до &lt; 200% дебиторская задолженность</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1539,7 +1539,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>KoeTekLikOt&gt;=20DebZad</t>
+          <t>KoeTekLikOt&gt;=10Do&lt;20DebZad</t>
         </is>
       </c>
     </row>
@@ -1554,7 +1554,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>коэффициент текущей ликвидности от &gt; = 200% в % к общей задолженности</t>
+          <t>коэффициент текущей ликвидности от &gt; = 100% до &lt; 200% в % к общей задолженности</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>KoeTekLikOt&gt;=20V%KObsZad,KoeTekLikOt&gt;=20V%KObsZadKre</t>
+          <t>KoeTekLikOt&gt;=10Do&lt;20V%KObsZad,KoeTekLikOt&gt;=10Do&lt;20V%KObsZadKre</t>
         </is>
       </c>
     </row>
@@ -1579,7 +1579,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>коэффициент текущей ликвидности от &gt; = 200% кредиторская задолженность</t>
+          <t>коэффициент текущей ликвидности от &gt; = 100% до &lt; 200% кредиторская задолженность</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>KoeTekLikOt&gt;=20KreZad</t>
+          <t>KoeTekLikOt&gt;=10Do&lt;20KreZad</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>коэффициент текущей ликвидности от &gt; = 200% денежные средства и денежные эквиваленты</t>
+          <t>коэффициент текущей ликвидности от &gt; = 100% до &lt; 200% денежные средства и денежные эквиваленты</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1614,7 +1614,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>KoeTekLikOt&gt;=20DenSreIDenEkv</t>
+          <t>KoeTekLikOt&gt;=10Do&lt;20DenSreIDenEkv</t>
         </is>
       </c>
     </row>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>коэффициент текущей ликвидности от &gt; = 200% в % ко всем денежным средствам денежным эквивалентам</t>
+          <t>коэффициент текущей ликвидности от &gt; = 100% до &lt; 200% в % ко всем денежным средствам денежным эквивалентам</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -1639,13 +1639,13 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>KoeTekLikOt&gt;=20V%KoVsDenSreDenEkv</t>
+          <t>KoeTekLikOt&gt;=10Do&lt;20V%KoVsDenSreDenEkv</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>коэффициент текущей ликвидности от &gt; = 100% до &lt; 200% количество организаций (единиц)</t>
+          <t>коэффициент текущей ликвидности от &gt; = 200% количество организаций (единиц)</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -1664,13 +1664,13 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>KoeTekLikOt&gt;=10Do&lt;20KolOrg(ed</t>
+          <t>KoeTekLikOt&gt;=20KolOrg(ed</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>коэффициент текущей ликвидности от &gt; = 100% до &lt; 200% в % к общему количеству</t>
+          <t>коэффициент текущей ликвидности от &gt; = 200% в % к общему количеству</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -1689,13 +1689,13 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>KoeTekLikOt&gt;=10Do&lt;20V%KObsKol</t>
+          <t>KoeTekLikOt&gt;=20V%KObsKol</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
@@ -1704,7 +1704,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>коэффициент текущей ликвидности от &gt; = 100% до &lt; 200% дебиторская задолженность</t>
+          <t>коэффициент текущей ликвидности от &gt; = 200% дебиторская задолженность</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -1714,13 +1714,13 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>KoeTekLikOt&gt;=10Do&lt;20DebZad</t>
+          <t>KoeTekLikOt&gt;=20DebZad</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>коэффициент текущей ликвидности от &gt; = 100% до &lt; 200% в % к общей задолженности</t>
+          <t>коэффициент текущей ликвидности от &gt; = 200% в % к общей задолженности</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -1739,13 +1739,13 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>KoeTekLikOt&gt;=10Do&lt;20V%KObsZad,KoeTekLikOt&gt;=10Do&lt;20V%KObsZadKre</t>
+          <t>KoeTekLikOt&gt;=20V%KObsZad,KoeTekLikOt&gt;=20V%KObsZadKre</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
@@ -1754,7 +1754,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>коэффициент текущей ликвидности от &gt; = 100% до &lt; 200% кредиторская задолженность</t>
+          <t>коэффициент текущей ликвидности от &gt; = 200% кредиторская задолженность</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -1764,13 +1764,13 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>KoeTekLikOt&gt;=10Do&lt;20KreZad</t>
+          <t>KoeTekLikOt&gt;=20KreZad</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
@@ -1779,7 +1779,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>коэффициент текущей ликвидности от &gt; = 100% до &lt; 200% денежные средства и денежные эквиваленты</t>
+          <t>коэффициент текущей ликвидности от &gt; = 200% денежные средства и денежные эквиваленты</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -1789,13 +1789,13 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>KoeTekLikOt&gt;=10Do&lt;20DenSreIDenEkv</t>
+          <t>KoeTekLikOt&gt;=20DenSreIDenEkv</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>коэффициент текущей ликвидности от &gt; = 100% до &lt; 200% в % ко всем денежным средствам денежным эквивалентам</t>
+          <t>коэффициент текущей ликвидности от &gt; = 200% в % ко всем денежным средствам денежным эквивалентам</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>KoeTekLikOt&gt;=10Do&lt;20V%KoVsDenSreDenEkv</t>
+          <t>KoeTekLikOt&gt;=20V%KoVsDenSreDenEkv</t>
         </is>
       </c>
     </row>
@@ -1829,7 +1829,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>коэффициент текущей ликвидности от &gt; = 200% количество организаций (единиц)</t>
+          <t>коэффициент текущей ликвидности от &gt; = 100% до &lt; 200% количество организаций (единиц)</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -1839,7 +1839,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>KoeTekLikOt&gt;=20KolOrg(ed</t>
+          <t>KoeTekLikOt&gt;=10Do&lt;20KolOrg(ed</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>коэффициент текущей ликвидности от &gt; = 200% в % к общему количеству</t>
+          <t>коэффициент текущей ликвидности от &gt; = 100% до &lt; 200% в % к общему количеству</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -1864,7 +1864,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>KoeTekLikOt&gt;=20V%KObsKol</t>
+          <t>KoeTekLikOt&gt;=10Do&lt;20V%KObsKol</t>
         </is>
       </c>
     </row>
@@ -1879,7 +1879,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>коэффициент текущей ликвидности от &gt; = 200% дебиторская задолженность</t>
+          <t>коэффициент текущей ликвидности от &gt; = 100% до &lt; 200% дебиторская задолженность</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>KoeTekLikOt&gt;=20DebZad</t>
+          <t>KoeTekLikOt&gt;=10Do&lt;20DebZad</t>
         </is>
       </c>
     </row>
@@ -1904,7 +1904,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>коэффициент текущей ликвидности от &gt; = 200% в % к общей задолженности</t>
+          <t>коэффициент текущей ликвидности от &gt; = 100% до &lt; 200% в % к общей задолженности</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>KoeTekLikOt&gt;=20V%KObsZad,KoeTekLikOt&gt;=20V%KObsZadKre</t>
+          <t>KoeTekLikOt&gt;=10Do&lt;20V%KObsZad,KoeTekLikOt&gt;=10Do&lt;20V%KObsZadKre</t>
         </is>
       </c>
     </row>
@@ -1929,7 +1929,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>коэффициент текущей ликвидности от &gt; = 200% кредиторская задолженность</t>
+          <t>коэффициент текущей ликвидности от &gt; = 100% до &lt; 200% кредиторская задолженность</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -1939,7 +1939,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>KoeTekLikOt&gt;=20KreZad</t>
+          <t>KoeTekLikOt&gt;=10Do&lt;20KreZad</t>
         </is>
       </c>
     </row>
@@ -1954,7 +1954,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>коэффициент текущей ликвидности от &gt; = 200% денежные средства и денежные эквиваленты</t>
+          <t>коэффициент текущей ликвидности от &gt; = 100% до &lt; 200% денежные средства и денежные эквиваленты</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -1964,7 +1964,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>KoeTekLikOt&gt;=20DenSreIDenEkv</t>
+          <t>KoeTekLikOt&gt;=10Do&lt;20DenSreIDenEkv</t>
         </is>
       </c>
     </row>
@@ -1979,7 +1979,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>коэффициент текущей ликвидности от &gt; = 200% в % ко всем денежным средствам денежным эквивалентам</t>
+          <t>коэффициент текущей ликвидности от &gt; = 100% до &lt; 200% в % ко всем денежным средствам денежным эквивалентам</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -1989,13 +1989,13 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>KoeTekLikOt&gt;=20V%KoVsDenSreDenEkv</t>
+          <t>KoeTekLikOt&gt;=10Do&lt;20V%KoVsDenSreDenEkv</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
@@ -2045,7 +2045,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
@@ -2070,7 +2070,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
@@ -2095,7 +2095,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
@@ -2170,7 +2170,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
@@ -2179,7 +2179,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>коэффициент текущей ликвидности до &lt; 100% количество организаций (единиц)</t>
+          <t>коэффициент текущей ликвидности от &gt; = 200% количество организаций (единиц)</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -2189,13 +2189,13 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>KoeTekLikDo&lt;10KolOrg(ed</t>
+          <t>KoeTekLikOt&gt;=20KolOrg(ed</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>коэффициент текущей ликвидности до &lt; 100% в % к общему количеству</t>
+          <t>коэффициент текущей ликвидности от &gt; = 200% в % к общему количеству</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -2214,13 +2214,13 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>KoeTekLikDo&lt;10V%KObsKol</t>
+          <t>KoeTekLikOt&gt;=20V%KObsKol</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>коэффициент текущей ликвидности до &lt; 100% дебиторская задолженность</t>
+          <t>коэффициент текущей ликвидности от &gt; = 200% дебиторская задолженность</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -2239,13 +2239,13 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>KoeTekLikDo&lt;10DebZad</t>
+          <t>KoeTekLikOt&gt;=20DebZad</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
@@ -2254,7 +2254,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>коэффициент текущей ликвидности до &lt; 100% в % к общей задолженности</t>
+          <t>коэффициент текущей ликвидности от &gt; = 200% в % к общей задолженности</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -2264,13 +2264,13 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>KoeTekLikDo&lt;10V%KObsZad,KoeTekLikDo&lt;10V%KObsZadKre</t>
+          <t>KoeTekLikOt&gt;=20V%KObsZad,KoeTekLikOt&gt;=20V%KObsZadKre</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>коэффициент текущей ликвидности до &lt; 100% кредиторская задолженность</t>
+          <t>коэффициент текущей ликвидности от &gt; = 200% кредиторская задолженность</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -2289,13 +2289,13 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>KoeTekLikDo&lt;10KreZad</t>
+          <t>KoeTekLikOt&gt;=20KreZad</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>коэффициент текущей ликвидности до &lt; 100% денежные средства и денежные эквиваленты</t>
+          <t>коэффициент текущей ликвидности от &gt; = 200% денежные средства и денежные эквиваленты</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -2314,13 +2314,13 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>KoeTekLikDo&lt;10DenSreIDenEkv</t>
+          <t>KoeTekLikOt&gt;=20DenSreIDenEkv</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>коэффициент текущей ликвидности до &lt; 100% в % ко всем денежным средствам денежным эквивалентам</t>
+          <t>коэффициент текущей ликвидности от &gt; = 200% в % ко всем денежным средствам денежным эквивалентам</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -2339,7 +2339,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>KoeTekLikDo&lt;10V%KoVsDenSreDenEkv</t>
+          <t>KoeTekLikOt&gt;=20V%KoVsDenSreDenEkv</t>
         </is>
       </c>
     </row>
@@ -2354,7 +2354,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>коэффициент текущей ликвидности от &gt; = 200% количество организаций (единиц)</t>
+          <t>коэффициент текущей ликвидности до &lt; 100% количество организаций (единиц)</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -2364,7 +2364,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>KoeTekLikOt&gt;=20KolOrg(ed</t>
+          <t>KoeTekLikDo&lt;10KolOrg(ed</t>
         </is>
       </c>
     </row>
@@ -2379,7 +2379,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>коэффициент текущей ликвидности от &gt; = 200% в % к общему количеству</t>
+          <t>коэффициент текущей ликвидности до &lt; 100% в % к общему количеству</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -2389,7 +2389,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>KoeTekLikOt&gt;=20V%KObsKol</t>
+          <t>KoeTekLikDo&lt;10V%KObsKol</t>
         </is>
       </c>
     </row>
@@ -2404,7 +2404,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>коэффициент текущей ликвидности от &gt; = 200% дебиторская задолженность</t>
+          <t>коэффициент текущей ликвидности до &lt; 100% дебиторская задолженность</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>KoeTekLikOt&gt;=20DebZad</t>
+          <t>KoeTekLikDo&lt;10DebZad</t>
         </is>
       </c>
     </row>
@@ -2429,7 +2429,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>коэффициент текущей ликвидности от &gt; = 200% в % к общей задолженности</t>
+          <t>коэффициент текущей ликвидности до &lt; 100% в % к общей задолженности</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>KoeTekLikOt&gt;=20V%KObsZad,KoeTekLikOt&gt;=20V%KObsZadKre</t>
+          <t>KoeTekLikDo&lt;10V%KObsZad,KoeTekLikDo&lt;10V%KObsZadKre</t>
         </is>
       </c>
     </row>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>коэффициент текущей ликвидности от &gt; = 200% кредиторская задолженность</t>
+          <t>коэффициент текущей ликвидности до &lt; 100% кредиторская задолженность</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>KoeTekLikOt&gt;=20KreZad</t>
+          <t>KoeTekLikDo&lt;10KreZad</t>
         </is>
       </c>
     </row>
@@ -2479,7 +2479,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>коэффициент текущей ликвидности от &gt; = 200% денежные средства и денежные эквиваленты</t>
+          <t>коэффициент текущей ликвидности до &lt; 100% денежные средства и денежные эквиваленты</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -2489,7 +2489,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>KoeTekLikOt&gt;=20DenSreIDenEkv</t>
+          <t>KoeTekLikDo&lt;10DenSreIDenEkv</t>
         </is>
       </c>
     </row>
@@ -2504,7 +2504,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>коэффициент текущей ликвидности от &gt; = 200% в % ко всем денежным средствам денежным эквивалентам</t>
+          <t>коэффициент текущей ликвидности до &lt; 100% в % ко всем денежным средствам денежным эквивалентам</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -2514,13 +2514,13 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>KoeTekLikOt&gt;=20V%KoVsDenSreDenEkv</t>
+          <t>KoeTekLikDo&lt;10V%KoVsDenSreDenEkv</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
@@ -2529,7 +2529,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>коэффициент текущей ликвидности до &lt; 100% количество организаций (единиц)</t>
+          <t>коэффициент текущей ликвидности от &gt; = 200% количество организаций (единиц)</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -2539,13 +2539,13 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>KoeTekLikDo&lt;10KolOrg(ed</t>
+          <t>KoeTekLikOt&gt;=20KolOrg(ed</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>коэффициент текущей ликвидности до &lt; 100% в % к общему количеству</t>
+          <t>коэффициент текущей ликвидности от &gt; = 200% в % к общему количеству</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -2564,13 +2564,13 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>KoeTekLikDo&lt;10V%KObsKol</t>
+          <t>KoeTekLikOt&gt;=20V%KObsKol</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
@@ -2579,7 +2579,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>коэффициент текущей ликвидности до &lt; 100% дебиторская задолженность</t>
+          <t>коэффициент текущей ликвидности от &gt; = 200% дебиторская задолженность</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -2589,13 +2589,13 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>KoeTekLikDo&lt;10DebZad</t>
+          <t>KoeTekLikOt&gt;=20DebZad</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>коэффициент текущей ликвидности до &lt; 100% в % к общей задолженности</t>
+          <t>коэффициент текущей ликвидности от &gt; = 200% в % к общей задолженности</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -2614,13 +2614,13 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>KoeTekLikDo&lt;10V%KObsZad,KoeTekLikDo&lt;10V%KObsZadKre</t>
+          <t>KoeTekLikOt&gt;=20V%KObsZad,KoeTekLikOt&gt;=20V%KObsZadKre</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
@@ -2629,7 +2629,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>коэффициент текущей ликвидности до &lt; 100% кредиторская задолженность</t>
+          <t>коэффициент текущей ликвидности от &gt; = 200% кредиторская задолженность</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -2639,13 +2639,13 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>KoeTekLikDo&lt;10KreZad</t>
+          <t>KoeTekLikOt&gt;=20KreZad</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
@@ -2654,7 +2654,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>коэффициент текущей ликвидности до &lt; 100% денежные средства и денежные эквиваленты</t>
+          <t>коэффициент текущей ликвидности от &gt; = 200% денежные средства и денежные эквиваленты</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -2664,13 +2664,13 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>KoeTekLikDo&lt;10DenSreIDenEkv</t>
+          <t>KoeTekLikOt&gt;=20DenSreIDenEkv</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
@@ -2679,7 +2679,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>коэффициент текущей ликвидности до &lt; 100% в % ко всем денежным средствам денежным эквивалентам</t>
+          <t>коэффициент текущей ликвидности от &gt; = 200% в % ко всем денежным средствам денежным эквивалентам</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -2689,7 +2689,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>KoeTekLikDo&lt;10V%KoVsDenSreDenEkv</t>
+          <t>KoeTekLikOt&gt;=20V%KoVsDenSreDenEkv</t>
         </is>
       </c>
     </row>
@@ -2704,7 +2704,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>коэффициент текущей ликвидности от &gt; = 200% количество организаций (единиц)</t>
+          <t>коэффициент текущей ликвидности до &lt; 100% количество организаций (единиц)</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -2714,7 +2714,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>KoeTekLikOt&gt;=20KolOrg(ed</t>
+          <t>KoeTekLikDo&lt;10KolOrg(ed</t>
         </is>
       </c>
     </row>
@@ -2729,7 +2729,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>коэффициент текущей ликвидности от &gt; = 200% в % к общему количеству</t>
+          <t>коэффициент текущей ликвидности до &lt; 100% в % к общему количеству</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -2739,7 +2739,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>KoeTekLikOt&gt;=20V%KObsKol</t>
+          <t>KoeTekLikDo&lt;10V%KObsKol</t>
         </is>
       </c>
     </row>
@@ -2754,7 +2754,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>коэффициент текущей ликвидности от &gt; = 200% дебиторская задолженность</t>
+          <t>коэффициент текущей ликвидности до &lt; 100% дебиторская задолженность</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -2764,7 +2764,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>KoeTekLikOt&gt;=20DebZad</t>
+          <t>KoeTekLikDo&lt;10DebZad</t>
         </is>
       </c>
     </row>
@@ -2779,7 +2779,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>коэффициент текущей ликвидности от &gt; = 200% в % к общей задолженности</t>
+          <t>коэффициент текущей ликвидности до &lt; 100% в % к общей задолженности</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -2789,7 +2789,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>KoeTekLikOt&gt;=20V%KObsZad,KoeTekLikOt&gt;=20V%KObsZadKre</t>
+          <t>KoeTekLikDo&lt;10V%KObsZad,KoeTekLikDo&lt;10V%KObsZadKre</t>
         </is>
       </c>
     </row>
@@ -2804,7 +2804,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>коэффициент текущей ликвидности от &gt; = 200% кредиторская задолженность</t>
+          <t>коэффициент текущей ликвидности до &lt; 100% кредиторская задолженность</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -2814,7 +2814,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>KoeTekLikOt&gt;=20KreZad</t>
+          <t>KoeTekLikDo&lt;10KreZad</t>
         </is>
       </c>
     </row>
@@ -2829,7 +2829,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>коэффициент текущей ликвидности от &gt; = 200% денежные средства и денежные эквиваленты</t>
+          <t>коэффициент текущей ликвидности до &lt; 100% денежные средства и денежные эквиваленты</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -2839,7 +2839,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>KoeTekLikOt&gt;=20DenSreIDenEkv</t>
+          <t>KoeTekLikDo&lt;10DenSreIDenEkv</t>
         </is>
       </c>
     </row>
@@ -2854,7 +2854,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>коэффициент текущей ликвидности от &gt; = 200% в % ко всем денежным средствам денежным эквивалентам</t>
+          <t>коэффициент текущей ликвидности до &lt; 100% в % ко всем денежным средствам денежным эквивалентам</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -2864,13 +2864,13 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>KoeTekLikOt&gt;=20V%KoVsDenSreDenEkv</t>
+          <t>KoeTekLikDo&lt;10V%KoVsDenSreDenEkv</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
@@ -2879,7 +2879,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>коэффициент текущей ликвидности до &lt; 100% количество организаций (единиц)</t>
+          <t>коэффициент текущей ликвидности от &gt; = 200% количество организаций (единиц)</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -2889,13 +2889,13 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>KoeTekLikDo&lt;10KolOrg(ed</t>
+          <t>KoeTekLikOt&gt;=20KolOrg(ed</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>коэффициент текущей ликвидности до &lt; 100% в % к общему количеству</t>
+          <t>коэффициент текущей ликвидности от &gt; = 200% в % к общему количеству</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -2914,13 +2914,13 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>KoeTekLikDo&lt;10V%KObsKol</t>
+          <t>KoeTekLikOt&gt;=20V%KObsKol</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>коэффициент текущей ликвидности до &lt; 100% дебиторская задолженность</t>
+          <t>коэффициент текущей ликвидности от &gt; = 200% дебиторская задолженность</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -2939,13 +2939,13 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>KoeTekLikDo&lt;10DebZad</t>
+          <t>KoeTekLikOt&gt;=20DebZad</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
@@ -2954,7 +2954,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>коэффициент текущей ликвидности до &lt; 100% в % к общей задолженности</t>
+          <t>коэффициент текущей ликвидности от &gt; = 200% в % к общей задолженности</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -2964,13 +2964,13 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>KoeTekLikDo&lt;10V%KObsZad,KoeTekLikDo&lt;10V%KObsZadKre</t>
+          <t>KoeTekLikOt&gt;=20V%KObsZad,KoeTekLikOt&gt;=20V%KObsZadKre</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
@@ -2979,7 +2979,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>коэффициент текущей ликвидности до &lt; 100% кредиторская задолженность</t>
+          <t>коэффициент текущей ликвидности от &gt; = 200% кредиторская задолженность</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -2989,13 +2989,13 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>KoeTekLikDo&lt;10KreZad</t>
+          <t>KoeTekLikOt&gt;=20KreZad</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B104" t="inlineStr">
         <is>
@@ -3004,7 +3004,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>коэффициент текущей ликвидности до &lt; 100% денежные средства и денежные эквиваленты</t>
+          <t>коэффициент текущей ликвидности от &gt; = 200% денежные средства и денежные эквиваленты</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -3014,13 +3014,13 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>KoeTekLikDo&lt;10DenSreIDenEkv</t>
+          <t>KoeTekLikOt&gt;=20DenSreIDenEkv</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B105" t="inlineStr">
         <is>
@@ -3029,7 +3029,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>коэффициент текущей ликвидности до &lt; 100% в % ко всем денежным средствам денежным эквивалентам</t>
+          <t>коэффициент текущей ликвидности от &gt; = 200% в % ко всем денежным средствам денежным эквивалентам</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -3039,7 +3039,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>KoeTekLikDo&lt;10V%KoVsDenSreDenEkv</t>
+          <t>KoeTekLikOt&gt;=20V%KoVsDenSreDenEkv</t>
         </is>
       </c>
     </row>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>коэффициент текущей ликвидности от &gt; = 200% количество организаций (единиц)</t>
+          <t>коэффициент текущей ликвидности до &lt; 100% количество организаций (единиц)</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -3064,7 +3064,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>KoeTekLikOt&gt;=20KolOrg(ed</t>
+          <t>KoeTekLikDo&lt;10KolOrg(ed</t>
         </is>
       </c>
     </row>
@@ -3079,7 +3079,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>коэффициент текущей ликвидности от &gt; = 200% в % к общему количеству</t>
+          <t>коэффициент текущей ликвидности до &lt; 100% в % к общему количеству</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -3089,7 +3089,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>KoeTekLikOt&gt;=20V%KObsKol</t>
+          <t>KoeTekLikDo&lt;10V%KObsKol</t>
         </is>
       </c>
     </row>
@@ -3104,7 +3104,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>коэффициент текущей ликвидности от &gt; = 200% дебиторская задолженность</t>
+          <t>коэффициент текущей ликвидности до &lt; 100% дебиторская задолженность</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>KoeTekLikOt&gt;=20DebZad</t>
+          <t>KoeTekLikDo&lt;10DebZad</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>коэффициент текущей ликвидности от &gt; = 200% в % к общей задолженности</t>
+          <t>коэффициент текущей ликвидности до &lt; 100% в % к общей задолженности</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -3139,7 +3139,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>KoeTekLikOt&gt;=20V%KObsZad,KoeTekLikOt&gt;=20V%KObsZadKre</t>
+          <t>KoeTekLikDo&lt;10V%KObsZad,KoeTekLikDo&lt;10V%KObsZadKre</t>
         </is>
       </c>
     </row>
@@ -3154,7 +3154,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>коэффициент текущей ликвидности от &gt; = 200% кредиторская задолженность</t>
+          <t>коэффициент текущей ликвидности до &lt; 100% кредиторская задолженность</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -3164,7 +3164,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>KoeTekLikOt&gt;=20KreZad</t>
+          <t>KoeTekLikDo&lt;10KreZad</t>
         </is>
       </c>
     </row>
@@ -3179,7 +3179,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>коэффициент текущей ликвидности от &gt; = 200% денежные средства и денежные эквиваленты</t>
+          <t>коэффициент текущей ликвидности до &lt; 100% денежные средства и денежные эквиваленты</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -3189,7 +3189,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>KoeTekLikOt&gt;=20DenSreIDenEkv</t>
+          <t>KoeTekLikDo&lt;10DenSreIDenEkv</t>
         </is>
       </c>
     </row>
@@ -3204,7 +3204,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>коэффициент текущей ликвидности от &gt; = 200% в % ко всем денежным средствам денежным эквивалентам</t>
+          <t>коэффициент текущей ликвидности до &lt; 100% в % ко всем денежным средствам денежным эквивалентам</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -3214,13 +3214,13 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>KoeTekLikOt&gt;=20V%KoVsDenSreDenEkv</t>
+          <t>KoeTekLikDo&lt;10V%KoVsDenSreDenEkv</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B113" t="inlineStr">
         <is>
@@ -3229,7 +3229,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>коэффициент текущей ликвидности до &lt; 100% количество организаций (единиц)</t>
+          <t>коэффициент текущей ликвидности от &gt; = 200% количество организаций (единиц)</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -3239,13 +3239,13 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>KoeTekLikDo&lt;10KolOrg(ed</t>
+          <t>KoeTekLikOt&gt;=20KolOrg(ed</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B114" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>коэффициент текущей ликвидности до &lt; 100% в % к общему количеству</t>
+          <t>коэффициент текущей ликвидности от &gt; = 200% в % к общему количеству</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -3264,13 +3264,13 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>KoeTekLikDo&lt;10V%KObsKol</t>
+          <t>KoeTekLikOt&gt;=20V%KObsKol</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B115" t="inlineStr">
         <is>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>коэффициент текущей ликвидности до &lt; 100% дебиторская задолженность</t>
+          <t>коэффициент текущей ликвидности от &gt; = 200% дебиторская задолженность</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -3289,13 +3289,13 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>KoeTekLikDo&lt;10DebZad</t>
+          <t>KoeTekLikOt&gt;=20DebZad</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B116" t="inlineStr">
         <is>
@@ -3304,7 +3304,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>коэффициент текущей ликвидности до &lt; 100% в % к общей задолженности</t>
+          <t>коэффициент текущей ликвидности от &gt; = 200% в % к общей задолженности</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -3314,13 +3314,13 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>KoeTekLikDo&lt;10V%KObsZad,KoeTekLikDo&lt;10V%KObsZadKre</t>
+          <t>KoeTekLikOt&gt;=20V%KObsZad,KoeTekLikOt&gt;=20V%KObsZadKre</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B117" t="inlineStr">
         <is>
@@ -3329,7 +3329,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>коэффициент текущей ликвидности до &lt; 100% кредиторская задолженность</t>
+          <t>коэффициент текущей ликвидности от &gt; = 200% кредиторская задолженность</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -3339,13 +3339,13 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>KoeTekLikDo&lt;10KreZad</t>
+          <t>KoeTekLikOt&gt;=20KreZad</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B118" t="inlineStr">
         <is>
@@ -3354,7 +3354,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>коэффициент текущей ликвидности до &lt; 100% денежные средства и денежные эквиваленты</t>
+          <t>коэффициент текущей ликвидности от &gt; = 200% денежные средства и денежные эквиваленты</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -3364,13 +3364,13 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>KoeTekLikDo&lt;10DenSreIDenEkv</t>
+          <t>KoeTekLikOt&gt;=20DenSreIDenEkv</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B119" t="inlineStr">
         <is>
@@ -3379,7 +3379,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>коэффициент текущей ликвидности до &lt; 100% в % ко всем денежным средствам денежным эквивалентам</t>
+          <t>коэффициент текущей ликвидности от &gt; = 200% в % ко всем денежным средствам денежным эквивалентам</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -3389,7 +3389,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>KoeTekLikDo&lt;10V%KoVsDenSreDenEkv</t>
+          <t>KoeTekLikOt&gt;=20V%KoVsDenSreDenEkv</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>коэффициент текущей ликвидности от &gt; = 100% до &lt; 200% количество организаций (единиц)</t>
+          <t>коэффициент текущей ликвидности до &lt; 100% количество организаций (единиц)</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -3414,7 +3414,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>KoeTekLikOt&gt;=10Do&lt;20KolOrg(ed</t>
+          <t>KoeTekLikDo&lt;10KolOrg(ed</t>
         </is>
       </c>
     </row>
@@ -3429,7 +3429,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>коэффициент текущей ликвидности от &gt; = 100% до &lt; 200% в % к общему количеству</t>
+          <t>коэффициент текущей ликвидности до &lt; 100% в % к общему количеству</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -3439,7 +3439,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>KoeTekLikOt&gt;=10Do&lt;20V%KObsKol</t>
+          <t>KoeTekLikDo&lt;10V%KObsKol</t>
         </is>
       </c>
     </row>
@@ -3454,7 +3454,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>коэффициент текущей ликвидности от &gt; = 100% до &lt; 200% дебиторская задолженность</t>
+          <t>коэффициент текущей ликвидности до &lt; 100% дебиторская задолженность</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -3464,7 +3464,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>KoeTekLikOt&gt;=10Do&lt;20DebZad</t>
+          <t>KoeTekLikDo&lt;10DebZad</t>
         </is>
       </c>
     </row>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>коэффициент текущей ликвидности от &gt; = 100% до &lt; 200% в % к общей задолженности</t>
+          <t>коэффициент текущей ликвидности до &lt; 100% в % к общей задолженности</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -3489,7 +3489,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>KoeTekLikOt&gt;=10Do&lt;20V%KObsZad,KoeTekLikOt&gt;=10Do&lt;20V%KObsZadKre</t>
+          <t>KoeTekLikDo&lt;10V%KObsZad,KoeTekLikDo&lt;10V%KObsZadKre</t>
         </is>
       </c>
     </row>
@@ -3504,7 +3504,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>коэффициент текущей ликвидности от &gt; = 100% до &lt; 200% кредиторская задолженность</t>
+          <t>коэффициент текущей ликвидности до &lt; 100% кредиторская задолженность</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>KoeTekLikOt&gt;=10Do&lt;20KreZad</t>
+          <t>KoeTekLikDo&lt;10KreZad</t>
         </is>
       </c>
     </row>
@@ -3529,7 +3529,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>коэффициент текущей ликвидности от &gt; = 100% до &lt; 200% денежные средства и денежные эквиваленты</t>
+          <t>коэффициент текущей ликвидности до &lt; 100% денежные средства и денежные эквиваленты</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -3539,7 +3539,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>KoeTekLikOt&gt;=10Do&lt;20DenSreIDenEkv</t>
+          <t>KoeTekLikDo&lt;10DenSreIDenEkv</t>
         </is>
       </c>
     </row>
@@ -3554,7 +3554,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>коэффициент текущей ликвидности от &gt; = 100% до &lt; 200% в % ко всем денежным средствам денежным эквивалентам</t>
+          <t>коэффициент текущей ликвидности до &lt; 100% в % ко всем денежным средствам денежным эквивалентам</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -3564,13 +3564,13 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>KoeTekLikOt&gt;=10Do&lt;20V%KoVsDenSreDenEkv</t>
+          <t>KoeTekLikDo&lt;10V%KoVsDenSreDenEkv</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B127" t="inlineStr">
         <is>
@@ -3579,7 +3579,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>коэффициент текущей ликвидности до &lt; 100% количество организаций (единиц)</t>
+          <t>коэффициент текущей ликвидности от &gt; = 100% до &lt; 200% количество организаций (единиц)</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -3589,13 +3589,13 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>KoeTekLikDo&lt;10KolOrg(ed</t>
+          <t>KoeTekLikOt&gt;=10Do&lt;20KolOrg(ed</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B128" t="inlineStr">
         <is>
@@ -3604,7 +3604,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>коэффициент текущей ликвидности до &lt; 100% в % к общему количеству</t>
+          <t>коэффициент текущей ликвидности от &gt; = 100% до &lt; 200% в % к общему количеству</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -3614,13 +3614,13 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>KoeTekLikDo&lt;10V%KObsKol</t>
+          <t>KoeTekLikOt&gt;=10Do&lt;20V%KObsKol</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B129" t="inlineStr">
         <is>
@@ -3629,7 +3629,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>коэффициент текущей ликвидности до &lt; 100% дебиторская задолженность</t>
+          <t>коэффициент текущей ликвидности от &gt; = 100% до &lt; 200% дебиторская задолженность</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -3639,13 +3639,13 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>KoeTekLikDo&lt;10DebZad</t>
+          <t>KoeTekLikOt&gt;=10Do&lt;20DebZad</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B130" t="inlineStr">
         <is>
@@ -3654,7 +3654,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>коэффициент текущей ликвидности до &lt; 100% в % к общей задолженности</t>
+          <t>коэффициент текущей ликвидности от &gt; = 100% до &lt; 200% в % к общей задолженности</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -3664,13 +3664,13 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>KoeTekLikDo&lt;10V%KObsZad,KoeTekLikDo&lt;10V%KObsZadKre</t>
+          <t>KoeTekLikOt&gt;=10Do&lt;20V%KObsZad,KoeTekLikOt&gt;=10Do&lt;20V%KObsZadKre</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B131" t="inlineStr">
         <is>
@@ -3679,7 +3679,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>коэффициент текущей ликвидности до &lt; 100% кредиторская задолженность</t>
+          <t>коэффициент текущей ликвидности от &gt; = 100% до &lt; 200% кредиторская задолженность</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -3689,13 +3689,13 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>KoeTekLikDo&lt;10KreZad</t>
+          <t>KoeTekLikOt&gt;=10Do&lt;20KreZad</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B132" t="inlineStr">
         <is>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>коэффициент текущей ликвидности до &lt; 100% денежные средства и денежные эквиваленты</t>
+          <t>коэффициент текущей ликвидности от &gt; = 100% до &lt; 200% денежные средства и денежные эквиваленты</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -3714,13 +3714,13 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>KoeTekLikDo&lt;10DenSreIDenEkv</t>
+          <t>KoeTekLikOt&gt;=10Do&lt;20DenSreIDenEkv</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B133" t="inlineStr">
         <is>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>коэффициент текущей ликвидности до &lt; 100% в % ко всем денежным средствам денежным эквивалентам</t>
+          <t>коэффициент текущей ликвидности от &gt; = 100% до &lt; 200% в % ко всем денежным средствам денежным эквивалентам</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -3739,7 +3739,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>KoeTekLikDo&lt;10V%KoVsDenSreDenEkv</t>
+          <t>KoeTekLikOt&gt;=10Do&lt;20V%KoVsDenSreDenEkv</t>
         </is>
       </c>
     </row>
@@ -3754,7 +3754,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>коэффициент текущей ликвидности от &gt; = 100% до &lt; 200% количество организаций (единиц)</t>
+          <t>коэффициент текущей ликвидности до &lt; 100% количество организаций (единиц)</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -3764,7 +3764,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>KoeTekLikOt&gt;=10Do&lt;20KolOrg(ed</t>
+          <t>KoeTekLikDo&lt;10KolOrg(ed</t>
         </is>
       </c>
     </row>
@@ -3779,7 +3779,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>коэффициент текущей ликвидности от &gt; = 100% до &lt; 200% в % к общему количеству</t>
+          <t>коэффициент текущей ликвидности до &lt; 100% в % к общему количеству</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -3789,7 +3789,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>KoeTekLikOt&gt;=10Do&lt;20V%KObsKol</t>
+          <t>KoeTekLikDo&lt;10V%KObsKol</t>
         </is>
       </c>
     </row>
@@ -3804,7 +3804,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>коэффициент текущей ликвидности от &gt; = 100% до &lt; 200% дебиторская задолженность</t>
+          <t>коэффициент текущей ликвидности до &lt; 100% дебиторская задолженность</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -3814,7 +3814,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>KoeTekLikOt&gt;=10Do&lt;20DebZad</t>
+          <t>KoeTekLikDo&lt;10DebZad</t>
         </is>
       </c>
     </row>
@@ -3829,7 +3829,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>коэффициент текущей ликвидности от &gt; = 100% до &lt; 200% в % к общей задолженности</t>
+          <t>коэффициент текущей ликвидности до &lt; 100% в % к общей задолженности</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -3839,7 +3839,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>KoeTekLikOt&gt;=10Do&lt;20V%KObsZad,KoeTekLikOt&gt;=10Do&lt;20V%KObsZadKre</t>
+          <t>KoeTekLikDo&lt;10V%KObsZad,KoeTekLikDo&lt;10V%KObsZadKre</t>
         </is>
       </c>
     </row>
@@ -3854,7 +3854,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>коэффициент текущей ликвидности от &gt; = 100% до &lt; 200% кредиторская задолженность</t>
+          <t>коэффициент текущей ликвидности до &lt; 100% кредиторская задолженность</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -3864,7 +3864,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>KoeTekLikOt&gt;=10Do&lt;20KreZad</t>
+          <t>KoeTekLikDo&lt;10KreZad</t>
         </is>
       </c>
     </row>
@@ -3879,7 +3879,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>коэффициент текущей ликвидности от &gt; = 100% до &lt; 200% денежные средства и денежные эквиваленты</t>
+          <t>коэффициент текущей ликвидности до &lt; 100% денежные средства и денежные эквиваленты</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -3889,7 +3889,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>KoeTekLikOt&gt;=10Do&lt;20DenSreIDenEkv</t>
+          <t>KoeTekLikDo&lt;10DenSreIDenEkv</t>
         </is>
       </c>
     </row>
@@ -3904,7 +3904,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>коэффициент текущей ликвидности от &gt; = 100% до &lt; 200% в % ко всем денежным средствам денежным эквивалентам</t>
+          <t>коэффициент текущей ликвидности до &lt; 100% в % ко всем денежным средствам денежным эквивалентам</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -3914,13 +3914,13 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>KoeTekLikOt&gt;=10Do&lt;20V%KoVsDenSreDenEkv</t>
+          <t>KoeTekLikDo&lt;10V%KoVsDenSreDenEkv</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B141" t="inlineStr">
         <is>
@@ -3929,7 +3929,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>коэффициент текущей ликвидности до &lt; 100% количество организаций (единиц)</t>
+          <t>коэффициент текущей ликвидности от &gt; = 100% до &lt; 200% количество организаций (единиц)</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -3939,13 +3939,13 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>KoeTekLikDo&lt;10KolOrg(ed</t>
+          <t>KoeTekLikOt&gt;=10Do&lt;20KolOrg(ed</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B142" t="inlineStr">
         <is>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>коэффициент текущей ликвидности до &lt; 100% в % к общему количеству</t>
+          <t>коэффициент текущей ликвидности от &gt; = 100% до &lt; 200% в % к общему количеству</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -3964,13 +3964,13 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>KoeTekLikDo&lt;10V%KObsKol</t>
+          <t>KoeTekLikOt&gt;=10Do&lt;20V%KObsKol</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B143" t="inlineStr">
         <is>
@@ -3979,7 +3979,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>коэффициент текущей ликвидности до &lt; 100% дебиторская задолженность</t>
+          <t>коэффициент текущей ликвидности от &gt; = 100% до &lt; 200% дебиторская задолженность</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -3989,13 +3989,13 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>KoeTekLikDo&lt;10DebZad</t>
+          <t>KoeTekLikOt&gt;=10Do&lt;20DebZad</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B144" t="inlineStr">
         <is>
@@ -4004,7 +4004,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>коэффициент текущей ликвидности до &lt; 100% в % к общей задолженности</t>
+          <t>коэффициент текущей ликвидности от &gt; = 100% до &lt; 200% в % к общей задолженности</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -4014,13 +4014,13 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>KoeTekLikDo&lt;10V%KObsZad,KoeTekLikDo&lt;10V%KObsZadKre</t>
+          <t>KoeTekLikOt&gt;=10Do&lt;20V%KObsZad,KoeTekLikOt&gt;=10Do&lt;20V%KObsZadKre</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B145" t="inlineStr">
         <is>
@@ -4029,7 +4029,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>коэффициент текущей ликвидности до &lt; 100% кредиторская задолженность</t>
+          <t>коэффициент текущей ликвидности от &gt; = 100% до &lt; 200% кредиторская задолженность</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -4039,13 +4039,13 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>KoeTekLikDo&lt;10KreZad</t>
+          <t>KoeTekLikOt&gt;=10Do&lt;20KreZad</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B146" t="inlineStr">
         <is>
@@ -4054,7 +4054,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>коэффициент текущей ликвидности до &lt; 100% денежные средства и денежные эквиваленты</t>
+          <t>коэффициент текущей ликвидности от &gt; = 100% до &lt; 200% денежные средства и денежные эквиваленты</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -4064,13 +4064,13 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>KoeTekLikDo&lt;10DenSreIDenEkv</t>
+          <t>KoeTekLikOt&gt;=10Do&lt;20DenSreIDenEkv</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B147" t="inlineStr">
         <is>
@@ -4079,7 +4079,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>коэффициент текущей ликвидности до &lt; 100% в % ко всем денежным средствам денежным эквивалентам</t>
+          <t>коэффициент текущей ликвидности от &gt; = 100% до &lt; 200% в % ко всем денежным средствам денежным эквивалентам</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -4089,7 +4089,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>KoeTekLikDo&lt;10V%KoVsDenSreDenEkv</t>
+          <t>KoeTekLikOt&gt;=10Do&lt;20V%KoVsDenSreDenEkv</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>коэффициент текущей ликвидности от &gt; = 100% до &lt; 200% количество организаций (единиц)</t>
+          <t>коэффициент текущей ликвидности до &lt; 100% количество организаций (единиц)</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -4114,7 +4114,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>KoeTekLikOt&gt;=10Do&lt;20KolOrg(ed</t>
+          <t>KoeTekLikDo&lt;10KolOrg(ed</t>
         </is>
       </c>
     </row>
@@ -4129,7 +4129,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>коэффициент текущей ликвидности от &gt; = 100% до &lt; 200% в % к общему количеству</t>
+          <t>коэффициент текущей ликвидности до &lt; 100% в % к общему количеству</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -4139,7 +4139,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>KoeTekLikOt&gt;=10Do&lt;20V%KObsKol</t>
+          <t>KoeTekLikDo&lt;10V%KObsKol</t>
         </is>
       </c>
     </row>
@@ -4154,7 +4154,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>коэффициент текущей ликвидности от &gt; = 100% до &lt; 200% дебиторская задолженность</t>
+          <t>коэффициент текущей ликвидности до &lt; 100% дебиторская задолженность</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -4164,7 +4164,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>KoeTekLikOt&gt;=10Do&lt;20DebZad</t>
+          <t>KoeTekLikDo&lt;10DebZad</t>
         </is>
       </c>
     </row>
@@ -4179,7 +4179,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>коэффициент текущей ликвидности от &gt; = 100% до &lt; 200% в % к общей задолженности</t>
+          <t>коэффициент текущей ликвидности до &lt; 100% в % к общей задолженности</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -4189,7 +4189,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>KoeTekLikOt&gt;=10Do&lt;20V%KObsZad,KoeTekLikOt&gt;=10Do&lt;20V%KObsZadKre</t>
+          <t>KoeTekLikDo&lt;10V%KObsZad,KoeTekLikDo&lt;10V%KObsZadKre</t>
         </is>
       </c>
     </row>
@@ -4204,7 +4204,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>коэффициент текущей ликвидности от &gt; = 100% до &lt; 200% кредиторская задолженность</t>
+          <t>коэффициент текущей ликвидности до &lt; 100% кредиторская задолженность</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>KoeTekLikOt&gt;=10Do&lt;20KreZad</t>
+          <t>KoeTekLikDo&lt;10KreZad</t>
         </is>
       </c>
     </row>
@@ -4229,7 +4229,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>коэффициент текущей ликвидности от &gt; = 100% до &lt; 200% денежные средства и денежные эквиваленты</t>
+          <t>коэффициент текущей ликвидности до &lt; 100% денежные средства и денежные эквиваленты</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>KoeTekLikOt&gt;=10Do&lt;20DenSreIDenEkv</t>
+          <t>KoeTekLikDo&lt;10DenSreIDenEkv</t>
         </is>
       </c>
     </row>
@@ -4254,7 +4254,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>коэффициент текущей ликвидности от &gt; = 100% до &lt; 200% в % ко всем денежным средствам денежным эквивалентам</t>
+          <t>коэффициент текущей ликвидности до &lt; 100% в % ко всем денежным средствам денежным эквивалентам</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -4264,188 +4264,188 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>KoeTekLikOt&gt;=10Do&lt;20V%KoVsDenSreDenEkv</t>
+          <t>KoeTekLikDo&lt;10V%KoVsDenSreDenEkv</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>T24_000000_t29Ved14.xlsx</t>
+          <t>T24_000000_t28Ved14.xlsx</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>поступления по текущей деятельности прочие поступления</t>
+          <t>коэффициент текущей ликвидности от &gt; = 100% до &lt; 200% количество организаций (единиц)</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>прочие поступления</t>
+          <t>количество организаций единиц</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>PrTekDeVsego</t>
+          <t>KoeTekLikOt&gt;=10Do&lt;20KolOrg(ed</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>T24_000000_t29Ved14.xlsx</t>
+          <t>T24_000000_t28Ved14.xlsx</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>платежи по текущей деятельности - всего</t>
+          <t>коэффициент текущей ликвидности от &gt; = 100% до &lt; 200% в % к общему количеству</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>всего</t>
+          <t>общему количеству</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>PlatPoTekDeVsego</t>
+          <t>KoeTekLikOt&gt;=10Do&lt;20V%KObsKol</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>T24_000000_t29Ved14.xlsx</t>
+          <t>T24_000000_t28Ved14.xlsx</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>платежи по инвестиционной деятельности - всего</t>
+          <t>коэффициент текущей ликвидности от &gt; = 100% до &lt; 200% дебиторская задолженность</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>всего</t>
+          <t>дебиторская задолженность</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>PlPoInvDeyt</t>
+          <t>KoeTekLikOt&gt;=10Do&lt;20DebZad</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>T24_000000_t29Ved14.xlsx</t>
+          <t>T24_000000_t28Ved14.xlsx</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>платежи по финансовой деятельности – всего</t>
+          <t>коэффициент текущей ликвидности от &gt; = 100% до &lt; 200% в % к общей задолженности</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>всего</t>
+          <t>общей задолженности</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>PlPoFin</t>
+          <t>KoeTekLikOt&gt;=10Do&lt;20V%KObsZad,KoeTekLikOt&gt;=10Do&lt;20V%KObsZadKre</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>T24_000000_t29Ved14.xlsx</t>
+          <t>T24_000000_t28Ved14.xlsx</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>поступления по текущей деятельности прочие поступления</t>
+          <t>коэффициент текущей ликвидности от &gt; = 100% до &lt; 200% кредиторская задолженность</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>прочие поступления</t>
+          <t>кредиторская задолженность</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>PrTekDeVsego</t>
+          <t>KoeTekLikOt&gt;=10Do&lt;20KreZad</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>T24_000000_t29Ved14.xlsx</t>
+          <t>T24_000000_t28Ved14.xlsx</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>платежи по текущей деятельности - всего</t>
+          <t>коэффициент текущей ликвидности от &gt; = 100% до &lt; 200% денежные средства и денежные эквиваленты</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>всего</t>
+          <t>денежные средства и денежные эквиваленты</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>PlatPoTekDeVsego</t>
+          <t>KoeTekLikOt&gt;=10Do&lt;20DenSreIDenEkv</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>T24_000000_t29Ved14.xlsx</t>
+          <t>T24_000000_t28Ved14.xlsx</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>платежи по инвестиционной деятельности - всего</t>
+          <t>коэффициент текущей ликвидности от &gt; = 100% до &lt; 200% в % ко всем денежным средствам денежным эквивалентам</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>всего</t>
+          <t>в ко всем денежным средствам денежным эквивалентам</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>PlPoInvDeyt</t>
+          <t>KoeTekLikOt&gt;=10Do&lt;20V%KoVsDenSreDenEkv</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B162" t="inlineStr">
         <is>
@@ -4454,23 +4454,23 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>платежи по финансовой деятельности – всего</t>
+          <t>поступления по текущей деятельности прочие поступления</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>всего</t>
+          <t>прочие поступления</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>PlPoFin</t>
+          <t>PrTekDeVsego</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B163" t="inlineStr">
         <is>
@@ -4479,23 +4479,23 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>поступления по текущей деятельности прочие поступления</t>
+          <t>платежи по текущей деятельности - всего</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>прочие поступления</t>
+          <t>всего</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>PrTekDeVsego</t>
+          <t>PlatPoTekDeVsego</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B164" t="inlineStr">
         <is>
@@ -4504,7 +4504,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>платежи по текущей деятельности - всего</t>
+          <t>платежи по инвестиционной деятельности - всего</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -4514,13 +4514,13 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>PlatPoTekDeVsego</t>
+          <t>PlPoInvDeyt</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B165" t="inlineStr">
         <is>
@@ -4529,7 +4529,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>платежи по инвестиционной деятельности - всего</t>
+          <t>платежи по финансовой деятельности – всего</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -4539,13 +4539,13 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>PlPoInvDeyt</t>
+          <t>PlPoFin</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B166" t="inlineStr">
         <is>
@@ -4554,23 +4554,23 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>платежи по финансовой деятельности – всего</t>
+          <t>поступления по текущей деятельности прочие поступления</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>всего</t>
+          <t>прочие поступления</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>PlPoFin</t>
+          <t>PrTekDeVsego</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B167" t="inlineStr">
         <is>
@@ -4579,23 +4579,23 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>поступления по текущей деятельности прочие поступления</t>
+          <t>платежи по текущей деятельности - всего</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>прочие поступления</t>
+          <t>всего</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>PrTekDeVsego</t>
+          <t>PlatPoTekDeVsego</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B168" t="inlineStr">
         <is>
@@ -4604,7 +4604,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>платежи по текущей деятельности - всего</t>
+          <t>платежи по инвестиционной деятельности - всего</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -4614,13 +4614,13 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>PlatPoTekDeVsego</t>
+          <t>PlPoInvDeyt</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B169" t="inlineStr">
         <is>
@@ -4629,7 +4629,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>платежи по инвестиционной деятельности - всего</t>
+          <t>платежи по финансовой деятельности – всего</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -4639,13 +4639,13 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>PlPoInvDeyt</t>
+          <t>PlPoFin</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B170" t="inlineStr">
         <is>
@@ -4654,23 +4654,23 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>платежи по финансовой деятельности – всего</t>
+          <t>поступления по текущей деятельности прочие поступления</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>всего</t>
+          <t>прочие поступления</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>PlPoFin</t>
+          <t>PrTekDeVsego</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B171" t="inlineStr">
         <is>
@@ -4679,23 +4679,23 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>поступления по текущей деятельности прочие поступления</t>
+          <t>платежи по текущей деятельности - всего</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>прочие поступления</t>
+          <t>всего</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>PrTekDeVsego</t>
+          <t>PlatPoTekDeVsego</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B172" t="inlineStr">
         <is>
@@ -4704,7 +4704,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>платежи по текущей деятельности - всего</t>
+          <t>платежи по инвестиционной деятельности - всего</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -4714,13 +4714,13 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>PlatPoTekDeVsego</t>
+          <t>PlPoInvDeyt</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B173" t="inlineStr">
         <is>
@@ -4729,7 +4729,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>платежи по инвестиционной деятельности - всего</t>
+          <t>платежи по финансовой деятельности – всего</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -4739,13 +4739,13 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>PlPoInvDeyt</t>
+          <t>PlPoFin</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B174" t="inlineStr">
         <is>
@@ -4754,23 +4754,23 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>платежи по финансовой деятельности – всего</t>
+          <t>поступления по текущей деятельности прочие поступления</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>всего</t>
+          <t>прочие поступления</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>PlPoFin</t>
+          <t>PrTekDeVsego</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B175" t="inlineStr">
         <is>
@@ -4779,23 +4779,23 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>поступления по текущей деятельности прочие поступления</t>
+          <t>платежи по текущей деятельности - всего</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>прочие поступления</t>
+          <t>всего</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>PrTekDeVsego</t>
+          <t>PlatPoTekDeVsego</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B176" t="inlineStr">
         <is>
@@ -4804,7 +4804,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>платежи по текущей деятельности - всего</t>
+          <t>платежи по инвестиционной деятельности - всего</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -4814,13 +4814,13 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>PlatPoTekDeVsego</t>
+          <t>PlPoInvDeyt</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B177" t="inlineStr">
         <is>
@@ -4829,7 +4829,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>платежи по инвестиционной деятельности - всего</t>
+          <t>платежи по финансовой деятельности – всего</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -4839,13 +4839,13 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>PlPoInvDeyt</t>
+          <t>PlPoFin</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B178" t="inlineStr">
         <is>
@@ -4854,23 +4854,23 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>платежи по финансовой деятельности – всего</t>
+          <t>поступления по текущей деятельности прочие поступления</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>всего</t>
+          <t>прочие поступления</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>PlPoFin</t>
+          <t>PrTekDeVsego</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B179" t="inlineStr">
         <is>
@@ -4879,7 +4879,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>поступления по текущей деятельности - всего</t>
+          <t>платежи по текущей деятельности - всего</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -4889,13 +4889,13 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>PostPoTekDeVsego</t>
+          <t>PlatPoTekDeVsego</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B180" t="inlineStr">
         <is>
@@ -4904,23 +4904,23 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>платежи по текущей деятельности прочие платежи</t>
+          <t>платежи по инвестиционной деятельности - всего</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>прочие платежи</t>
+          <t>всего</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>ProchiePlatezhi</t>
+          <t>PlPoInvDeyt</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B181" t="inlineStr">
         <is>
@@ -4929,7 +4929,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>платежи по инвестиционной деятельности - всего</t>
+          <t>платежи по финансовой деятельности – всего</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -4939,13 +4939,13 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>PlPoInvDeyt</t>
+          <t>PlPoFin</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B182" t="inlineStr">
         <is>
@@ -4954,23 +4954,23 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>платежи по инвестиционной деятельности прочие платежи</t>
+          <t>поступления по текущей деятельности прочие поступления</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>прочие платежи</t>
+          <t>прочие поступления</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>PrPl</t>
+          <t>PrTekDeVsego</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B183" t="inlineStr">
         <is>
@@ -4979,7 +4979,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>платежи по финансовой деятельности – всего</t>
+          <t>платежи по текущей деятельности - всего</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -4989,13 +4989,13 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>PlPoFin</t>
+          <t>PlatPoTekDeVsego</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B184" t="inlineStr">
         <is>
@@ -5004,23 +5004,23 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>платежи по финансовой деятельности прочие платежи</t>
+          <t>платежи по инвестиционной деятельности - всего</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>прочие платежи</t>
+          <t>всего</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>PrPoFin</t>
+          <t>PlPoInvDeyt</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B185" t="inlineStr">
         <is>
@@ -5029,7 +5029,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>поступления по текущей деятельности - всего</t>
+          <t>платежи по финансовой деятельности – всего</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -5039,13 +5039,13 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>PostPoTekDeVsego</t>
+          <t>PlPoFin</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B186" t="inlineStr">
         <is>
@@ -5054,23 +5054,23 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>платежи по текущей деятельности прочие платежи</t>
+          <t>поступления по текущей деятельности - всего</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>прочие платежи</t>
+          <t>всего</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>ProchiePlatezhi</t>
+          <t>PostPoTekDeVsego</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B187" t="inlineStr">
         <is>
@@ -5079,23 +5079,23 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>платежи по инвестиционной деятельности - всего</t>
+          <t>платежи по текущей деятельности прочие платежи</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>всего</t>
+          <t>прочие платежи</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>PlPoInvDeyt</t>
+          <t>ProchiePlatezhi</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B188" t="inlineStr">
         <is>
@@ -5104,23 +5104,23 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>платежи по инвестиционной деятельности прочие платежи</t>
+          <t>платежи по инвестиционной деятельности - всего</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>прочие платежи</t>
+          <t>всего</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>PrPl</t>
+          <t>PlPoInvDeyt</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B189" t="inlineStr">
         <is>
@@ -5129,23 +5129,23 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>платежи по финансовой деятельности – всего</t>
+          <t>платежи по инвестиционной деятельности прочие платежи</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>всего</t>
+          <t>прочие платежи</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>PlPoFin</t>
+          <t>PrPl</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B190" t="inlineStr">
         <is>
@@ -5154,23 +5154,23 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>платежи по финансовой деятельности прочие платежи</t>
+          <t>платежи по финансовой деятельности – всего</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>прочие платежи</t>
+          <t>всего</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>PrPoFin</t>
+          <t>PlPoFin</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B191" t="inlineStr">
         <is>
@@ -5179,23 +5179,23 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>поступления по текущей деятельности - всего</t>
+          <t>платежи по финансовой деятельности прочие платежи</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>всего</t>
+          <t>прочие платежи</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>PostPoTekDeVsego</t>
+          <t>PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B192" t="inlineStr">
         <is>
@@ -5204,23 +5204,23 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>платежи по текущей деятельности прочие платежи</t>
+          <t>поступления по текущей деятельности - всего</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>прочие платежи</t>
+          <t>всего</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>ProchiePlatezhi</t>
+          <t>PostPoTekDeVsego</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B193" t="inlineStr">
         <is>
@@ -5229,23 +5229,23 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>платежи по инвестиционной деятельности - всего</t>
+          <t>платежи по текущей деятельности прочие платежи</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>всего</t>
+          <t>прочие платежи</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>PlPoInvDeyt</t>
+          <t>ProchiePlatezhi</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B194" t="inlineStr">
         <is>
@@ -5254,23 +5254,23 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>платежи по инвестиционной деятельности прочие платежи</t>
+          <t>платежи по инвестиционной деятельности - всего</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>прочие платежи</t>
+          <t>всего</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>PrPl</t>
+          <t>PlPoInvDeyt</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B195" t="inlineStr">
         <is>
@@ -5279,23 +5279,23 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>платежи по финансовой деятельности – всего</t>
+          <t>платежи по инвестиционной деятельности прочие платежи</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>всего</t>
+          <t>прочие платежи</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>PlPoFin</t>
+          <t>PrPl</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B196" t="inlineStr">
         <is>
@@ -5304,23 +5304,23 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>платежи по финансовой деятельности прочие платежи</t>
+          <t>платежи по финансовой деятельности – всего</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>прочие платежи</t>
+          <t>всего</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>PrPoFin</t>
+          <t>PlPoFin</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B197" t="inlineStr">
         <is>
@@ -5329,23 +5329,23 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>поступления по текущей деятельности - всего</t>
+          <t>платежи по финансовой деятельности прочие платежи</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>всего</t>
+          <t>прочие платежи</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>PostPoTekDeVsego</t>
+          <t>PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B198" t="inlineStr">
         <is>
@@ -5354,23 +5354,23 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>платежи по текущей деятельности прочие платежи</t>
+          <t>поступления по текущей деятельности - всего</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>прочие платежи</t>
+          <t>всего</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>ProchiePlatezhi</t>
+          <t>PostPoTekDeVsego</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B199" t="inlineStr">
         <is>
@@ -5379,23 +5379,23 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>платежи по инвестиционной деятельности - всего</t>
+          <t>платежи по текущей деятельности прочие платежи</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>всего</t>
+          <t>прочие платежи</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>PlPoInvDeyt</t>
+          <t>ProchiePlatezhi</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B200" t="inlineStr">
         <is>
@@ -5404,23 +5404,23 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>платежи по инвестиционной деятельности прочие платежи</t>
+          <t>платежи по инвестиционной деятельности - всего</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>прочие платежи</t>
+          <t>всего</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>PrPl</t>
+          <t>PlPoInvDeyt</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B201" t="inlineStr">
         <is>
@@ -5429,23 +5429,23 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>платежи по финансовой деятельности – всего</t>
+          <t>платежи по инвестиционной деятельности прочие платежи</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>всего</t>
+          <t>прочие платежи</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>PlPoFin</t>
+          <t>PrPl</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B202" t="inlineStr">
         <is>
@@ -5454,23 +5454,23 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>платежи по финансовой деятельности прочие платежи</t>
+          <t>платежи по финансовой деятельности – всего</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>прочие платежи</t>
+          <t>всего</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>PrPoFin</t>
+          <t>PlPoFin</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B203" t="inlineStr">
         <is>
@@ -5479,23 +5479,23 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>поступления по текущей деятельности - всего</t>
+          <t>платежи по финансовой деятельности прочие платежи</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>всего</t>
+          <t>прочие платежи</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>PostPoTekDeVsego</t>
+          <t>PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B204" t="inlineStr">
         <is>
@@ -5504,23 +5504,23 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>поступления по текущей деятельности прочие поступления</t>
+          <t>поступления по текущей деятельности - всего</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>прочие поступления</t>
+          <t>всего</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>PrTekDeVsego</t>
+          <t>PostPoTekDeVsego</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B205" t="inlineStr">
         <is>
@@ -5529,23 +5529,23 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>платежи по текущей деятельности - всего</t>
+          <t>платежи по текущей деятельности прочие платежи</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>всего</t>
+          <t>прочие платежи</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>PlatPoTekDeVsego</t>
+          <t>ProchiePlatezhi</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B206" t="inlineStr">
         <is>
@@ -5570,7 +5570,7 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B207" t="inlineStr">
         <is>
@@ -5579,23 +5579,23 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>в связи с приобретением акций других организаций (долей участия)</t>
+          <t>платежи по инвестиционной деятельности прочие платежи</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>акций других организаций долей участия</t>
+          <t>прочие платежи</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>DolUch</t>
+          <t>PrPl</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B208" t="inlineStr">
         <is>
@@ -5620,7 +5620,7 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B209" t="inlineStr">
         <is>
@@ -5629,23 +5629,23 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>поступления по текущей деятельности - всего</t>
+          <t>платежи по финансовой деятельности прочие платежи</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>всего</t>
+          <t>прочие платежи</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>PostPoTekDeVsego</t>
+          <t>PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B210" t="inlineStr">
         <is>
@@ -5654,23 +5654,23 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>поступления по текущей деятельности прочие поступления</t>
+          <t>поступления по текущей деятельности - всего</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>прочие поступления</t>
+          <t>всего</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>PrTekDeVsego</t>
+          <t>PostPoTekDeVsego</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B211" t="inlineStr">
         <is>
@@ -5679,23 +5679,23 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>платежи по текущей деятельности - всего</t>
+          <t>поступления по текущей деятельности прочие поступления</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>всего</t>
+          <t>прочие поступления</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>PlatPoTekDeVsego</t>
+          <t>PrTekDeVsego</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B212" t="inlineStr">
         <is>
@@ -5704,7 +5704,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>платежи по инвестиционной деятельности - всего</t>
+          <t>платежи по текущей деятельности - всего</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -5714,13 +5714,13 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>PlPoInvDeyt</t>
+          <t>PlatPoTekDeVsego</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B213" t="inlineStr">
         <is>
@@ -5729,23 +5729,23 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>в связи с приобретением акций других организаций (долей участия)</t>
+          <t>платежи по инвестиционной деятельности - всего</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>акций других организаций долей участия</t>
+          <t>всего</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>DolUch</t>
+          <t>PlPoInvDeyt</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B214" t="inlineStr">
         <is>
@@ -5754,23 +5754,23 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>платежи по финансовой деятельности – всего</t>
+          <t>в связи с приобретением акций других организаций (долей участия)</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>всего</t>
+          <t>акций других организаций долей участия</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>PlPoFin</t>
+          <t>DolUch</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B215" t="inlineStr">
         <is>
@@ -5779,7 +5779,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>поступления по текущей деятельности - всего</t>
+          <t>платежи по финансовой деятельности – всего</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -5789,13 +5789,13 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>PostPoTekDeVsego</t>
+          <t>PlPoFin</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B216" t="inlineStr">
         <is>
@@ -5804,23 +5804,23 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>поступления по текущей деятельности прочие поступления</t>
+          <t>поступления по текущей деятельности - всего</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>прочие поступления</t>
+          <t>всего</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>PrTekDeVsego</t>
+          <t>PostPoTekDeVsego</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B217" t="inlineStr">
         <is>
@@ -5829,23 +5829,23 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>платежи по текущей деятельности - всего</t>
+          <t>поступления по текущей деятельности прочие поступления</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>всего</t>
+          <t>прочие поступления</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>PlatPoTekDeVsego</t>
+          <t>PrTekDeVsego</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B218" t="inlineStr">
         <is>
@@ -5854,7 +5854,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>платежи по инвестиционной деятельности - всего</t>
+          <t>платежи по текущей деятельности - всего</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -5864,13 +5864,13 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>PlPoInvDeyt</t>
+          <t>PlatPoTekDeVsego</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B219" t="inlineStr">
         <is>
@@ -5879,23 +5879,23 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>в связи с приобретением акций других организаций (долей участия)</t>
+          <t>платежи по инвестиционной деятельности - всего</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>акций других организаций долей участия</t>
+          <t>всего</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>DolUch</t>
+          <t>PlPoInvDeyt</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B220" t="inlineStr">
         <is>
@@ -5904,23 +5904,23 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>платежи по финансовой деятельности – всего</t>
+          <t>в связи с приобретением акций других организаций (долей участия)</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>всего</t>
+          <t>акций других организаций долей участия</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>PlPoFin</t>
+          <t>DolUch</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B221" t="inlineStr">
         <is>
@@ -5929,7 +5929,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>поступления по текущей деятельности - всего</t>
+          <t>платежи по финансовой деятельности – всего</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -5939,13 +5939,13 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>PostPoTekDeVsego</t>
+          <t>PlPoFin</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B222" t="inlineStr">
         <is>
@@ -5954,23 +5954,23 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>поступления по текущей деятельности прочие поступления</t>
+          <t>поступления по текущей деятельности - всего</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>прочие поступления</t>
+          <t>всего</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>PrTekDeVsego</t>
+          <t>PostPoTekDeVsego</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B223" t="inlineStr">
         <is>
@@ -5979,23 +5979,23 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>платежи по текущей деятельности - всего</t>
+          <t>поступления по текущей деятельности прочие поступления</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>всего</t>
+          <t>прочие поступления</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>PlatPoTekDeVsego</t>
+          <t>PrTekDeVsego</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B224" t="inlineStr">
         <is>
@@ -6004,7 +6004,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>платежи по инвестиционной деятельности - всего</t>
+          <t>платежи по текущей деятельности - всего</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -6014,13 +6014,13 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>PlPoInvDeyt</t>
+          <t>PlatPoTekDeVsego</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B225" t="inlineStr">
         <is>
@@ -6029,23 +6029,23 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>в связи с приобретением акций других организаций (долей участия)</t>
+          <t>платежи по инвестиционной деятельности - всего</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>акций других организаций долей участия</t>
+          <t>всего</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>DolUch</t>
+          <t>PlPoInvDeyt</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B226" t="inlineStr">
         <is>
@@ -6054,23 +6054,23 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>платежи по финансовой деятельности – всего</t>
+          <t>в связи с приобретением акций других организаций (долей участия)</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>всего</t>
+          <t>акций других организаций долей участия</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>PlPoFin</t>
+          <t>DolUch</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B227" t="inlineStr">
         <is>
@@ -6079,7 +6079,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>поступления по текущей деятельности - всего</t>
+          <t>платежи по финансовой деятельности – всего</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -6089,13 +6089,13 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>PostPoTekDeVsego</t>
+          <t>PlPoFin</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B228" t="inlineStr">
         <is>
@@ -6104,7 +6104,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>платежи по текущей деятельности - всего</t>
+          <t>поступления по текущей деятельности - всего</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -6114,13 +6114,13 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>PlatPoTekDeVsego</t>
+          <t>PostPoTekDeVsego</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B229" t="inlineStr">
         <is>
@@ -6129,23 +6129,23 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>платежи по текущей деятельности прочие платежи</t>
+          <t>поступления по текущей деятельности прочие поступления</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>прочие платежи</t>
+          <t>прочие поступления</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>ProchiePlatezhi</t>
+          <t>PrTekDeVsego</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B230" t="inlineStr">
         <is>
@@ -6154,23 +6154,23 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>от продажи акций других организаций (долей участия)</t>
+          <t>платежи по текущей деятельности - всего</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>акций других организаций долей участия</t>
+          <t>всего</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>OtProdAkcOrgDolUch</t>
+          <t>PlatPoTekDeVsego</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B231" t="inlineStr">
         <is>
@@ -6179,23 +6179,23 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>платежи по инвестиционной деятельности прочие платежи</t>
+          <t>платежи по инвестиционной деятельности - всего</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>прочие платежи</t>
+          <t>всего</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>PrPl</t>
+          <t>PlPoInvDeyt</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B232" t="inlineStr">
         <is>
@@ -6204,23 +6204,23 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>платежи по финансовой деятельности – всего</t>
+          <t>в связи с приобретением акций других организаций (долей участия)</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>всего</t>
+          <t>акций других организаций долей участия</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>PlPoFin</t>
+          <t>DolUch</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B233" t="inlineStr">
         <is>
@@ -6229,23 +6229,23 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>платежи по финансовой деятельности прочие платежи</t>
+          <t>платежи по финансовой деятельности – всего</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>прочие платежи</t>
+          <t>всего</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>PrPoFin</t>
+          <t>PlPoFin</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B234" t="inlineStr">
         <is>
@@ -6270,7 +6270,7 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B235" t="inlineStr">
         <is>
@@ -6295,7 +6295,7 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B236" t="inlineStr">
         <is>
@@ -6320,7 +6320,7 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B237" t="inlineStr">
         <is>
@@ -6345,7 +6345,7 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B238" t="inlineStr">
         <is>
@@ -6370,7 +6370,7 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B239" t="inlineStr">
         <is>
@@ -6395,7 +6395,7 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B240" t="inlineStr">
         <is>
@@ -6420,7 +6420,7 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B241" t="inlineStr">
         <is>
@@ -6445,7 +6445,7 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B242" t="inlineStr">
         <is>
@@ -6470,7 +6470,7 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B243" t="inlineStr">
         <is>
@@ -6495,7 +6495,7 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B244" t="inlineStr">
         <is>
@@ -6520,7 +6520,7 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B245" t="inlineStr">
         <is>
@@ -6545,7 +6545,7 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B246" t="inlineStr">
         <is>
@@ -6570,7 +6570,7 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B247" t="inlineStr">
         <is>
@@ -6595,7 +6595,7 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B248" t="inlineStr">
         <is>
@@ -6620,7 +6620,7 @@
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B249" t="inlineStr">
         <is>
@@ -6645,7 +6645,7 @@
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B250" t="inlineStr">
         <is>
@@ -6670,7 +6670,7 @@
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B251" t="inlineStr">
         <is>
@@ -6695,7 +6695,7 @@
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B252" t="inlineStr">
         <is>
@@ -6720,7 +6720,7 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B253" t="inlineStr">
         <is>
@@ -6745,7 +6745,7 @@
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B254" t="inlineStr">
         <is>
@@ -6770,7 +6770,7 @@
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B255" t="inlineStr">
         <is>
@@ -6795,7 +6795,7 @@
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B256" t="inlineStr">
         <is>
@@ -6820,7 +6820,7 @@
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B257" t="inlineStr">
         <is>
@@ -6829,23 +6829,23 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>платежи по инвестиционной деятельности - всего</t>
+          <t>платежи по текущей деятельности прочие платежи</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>всего</t>
+          <t>прочие платежи</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>PlPoInvDeyt</t>
+          <t>ProchiePlatezhi</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B258" t="inlineStr">
         <is>
@@ -6854,23 +6854,23 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>платежи по финансовой деятельности – всего</t>
+          <t>от продажи акций других организаций (долей участия)</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>всего</t>
+          <t>акций других организаций долей участия</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>PlPoFin</t>
+          <t>OtProdAkcOrgDolUch</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B259" t="inlineStr">
         <is>
@@ -6879,23 +6879,23 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>поступления по текущей деятельности - всего</t>
+          <t>платежи по инвестиционной деятельности прочие платежи</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>всего</t>
+          <t>прочие платежи</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>PostPoTekDeVsego</t>
+          <t>PrPl</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B260" t="inlineStr">
         <is>
@@ -6904,7 +6904,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>платежи по текущей деятельности - всего</t>
+          <t>платежи по финансовой деятельности – всего</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -6914,13 +6914,13 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>PlatPoTekDeVsego</t>
+          <t>PlPoFin</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B261" t="inlineStr">
         <is>
@@ -6929,23 +6929,23 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>платежи по инвестиционной деятельности - всего</t>
+          <t>платежи по финансовой деятельности прочие платежи</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>всего</t>
+          <t>прочие платежи</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>PlPoInvDeyt</t>
+          <t>PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B262" t="inlineStr">
         <is>
@@ -6954,7 +6954,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>платежи по финансовой деятельности – всего</t>
+          <t>поступления по текущей деятельности - всего</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -6964,13 +6964,13 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>PlPoFin</t>
+          <t>PostPoTekDeVsego</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B263" t="inlineStr">
         <is>
@@ -6979,7 +6979,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>поступления по текущей деятельности - всего</t>
+          <t>платежи по текущей деятельности - всего</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -6989,13 +6989,13 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>PostPoTekDeVsego</t>
+          <t>PlatPoTekDeVsego</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B264" t="inlineStr">
         <is>
@@ -7004,7 +7004,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>платежи по текущей деятельности - всего</t>
+          <t>платежи по инвестиционной деятельности - всего</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -7014,13 +7014,13 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>PlatPoTekDeVsego</t>
+          <t>PlPoInvDeyt</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B265" t="inlineStr">
         <is>
@@ -7029,23 +7029,23 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>платежи по текущей деятельности прочие платежи</t>
+          <t>платежи по финансовой деятельности – всего</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>прочие платежи</t>
+          <t>всего</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>ProchiePlatezhi</t>
+          <t>PlPoFin</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B266" t="inlineStr">
         <is>
@@ -7054,7 +7054,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>платежи по инвестиционной деятельности - всего</t>
+          <t>поступления по текущей деятельности - всего</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -7064,13 +7064,13 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>PlPoInvDeyt</t>
+          <t>PostPoTekDeVsego</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B267" t="inlineStr">
         <is>
@@ -7079,23 +7079,23 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>платежи по инвестиционной деятельности прочие платежи</t>
+          <t>платежи по текущей деятельности - всего</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>прочие платежи</t>
+          <t>всего</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>PrPl</t>
+          <t>PlatPoTekDeVsego</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B268" t="inlineStr">
         <is>
@@ -7104,23 +7104,23 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>платежи по финансовой деятельности прочие платежи</t>
+          <t>платежи по инвестиционной деятельности - всего</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>прочие платежи</t>
+          <t>всего</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>PrPoFin</t>
+          <t>PlPoInvDeyt</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B269" t="inlineStr">
         <is>
@@ -7129,7 +7129,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>поступления по текущей деятельности - всего</t>
+          <t>платежи по финансовой деятельности – всего</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -7139,13 +7139,13 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>PostPoTekDeVsego</t>
+          <t>PlPoFin</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B270" t="inlineStr">
         <is>
@@ -7154,7 +7154,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>платежи по текущей деятельности - всего</t>
+          <t>поступления по текущей деятельности - всего</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -7164,13 +7164,13 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>PlatPoTekDeVsego</t>
+          <t>PostPoTekDeVsego</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B271" t="inlineStr">
         <is>
@@ -7179,23 +7179,23 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>платежи по текущей деятельности прочие платежи</t>
+          <t>платежи по текущей деятельности - всего</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>прочие платежи</t>
+          <t>всего</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>ProchiePlatezhi</t>
+          <t>PlatPoTekDeVsego</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B272" t="inlineStr">
         <is>
@@ -7204,23 +7204,23 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>платежи по инвестиционной деятельности - всего</t>
+          <t>платежи по текущей деятельности прочие платежи</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>всего</t>
+          <t>прочие платежи</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>PlPoInvDeyt</t>
+          <t>ProchiePlatezhi</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B273" t="inlineStr">
         <is>
@@ -7229,23 +7229,23 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>платежи по инвестиционной деятельности прочие платежи</t>
+          <t>платежи по инвестиционной деятельности - всего</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>прочие платежи</t>
+          <t>всего</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>PrPl</t>
+          <t>PlPoInvDeyt</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B274" t="inlineStr">
         <is>
@@ -7254,23 +7254,23 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>поступления по финансовой деятельности - всего</t>
+          <t>платежи по инвестиционной деятельности прочие платежи</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>финансовой деятельности всего</t>
+          <t>прочие платежи</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>PostFin</t>
+          <t>PrPl</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B275" t="inlineStr">
         <is>
@@ -7295,7 +7295,7 @@
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B276" t="inlineStr">
         <is>
@@ -7320,7 +7320,7 @@
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B277" t="inlineStr">
         <is>
@@ -7345,7 +7345,7 @@
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B278" t="inlineStr">
         <is>
@@ -7370,7 +7370,7 @@
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B279" t="inlineStr">
         <is>
@@ -7395,7 +7395,7 @@
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B280" t="inlineStr">
         <is>
@@ -7420,7 +7420,7 @@
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B281" t="inlineStr">
         <is>
@@ -7445,7 +7445,7 @@
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B282" t="inlineStr">
         <is>
@@ -7470,7 +7470,7 @@
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B283" t="inlineStr">
         <is>
@@ -7495,7 +7495,7 @@
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B284" t="inlineStr">
         <is>
@@ -7520,7 +7520,7 @@
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B285" t="inlineStr">
         <is>
@@ -7529,23 +7529,23 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>платежи по инвестиционной деятельности - всего</t>
+          <t>платежи по текущей деятельности прочие платежи</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>всего</t>
+          <t>прочие платежи</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>PlPoInvDeyt</t>
+          <t>ProchiePlatezhi</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B286" t="inlineStr">
         <is>
@@ -7554,7 +7554,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>платежи по финансовой деятельности – всего</t>
+          <t>платежи по инвестиционной деятельности - всего</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -7564,13 +7564,13 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>PlPoFin</t>
+          <t>PlPoInvDeyt</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B287" t="inlineStr">
         <is>
@@ -7579,23 +7579,23 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>поступления по текущей деятельности - всего</t>
+          <t>платежи по инвестиционной деятельности прочие платежи</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>всего</t>
+          <t>прочие платежи</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>PostPoTekDeVsego</t>
+          <t>PrPl</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="n">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B288" t="inlineStr">
         <is>
@@ -7604,23 +7604,23 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>платежи по текущей деятельности - всего</t>
+          <t>поступления по финансовой деятельности - всего</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>всего</t>
+          <t>финансовой деятельности всего</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>PlatPoTekDeVsego</t>
+          <t>PostFin</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="n">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B289" t="inlineStr">
         <is>
@@ -7629,23 +7629,23 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>платежи по инвестиционной деятельности - всего</t>
+          <t>платежи по финансовой деятельности прочие платежи</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>всего</t>
+          <t>прочие платежи</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>PlPoInvDeyt</t>
+          <t>PrPoFin</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B290" t="inlineStr">
         <is>
@@ -7654,7 +7654,7 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>платежи по финансовой деятельности – всего</t>
+          <t>поступления по текущей деятельности - всего</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -7664,13 +7664,13 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>PlPoFin</t>
+          <t>PostPoTekDeVsego</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="n">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B291" t="inlineStr">
         <is>
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>поступления по текущей деятельности - всего</t>
+          <t>платежи по текущей деятельности - всего</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -7689,13 +7689,13 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>PostPoTekDeVsego</t>
+          <t>PlatPoTekDeVsego</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="n">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B292" t="inlineStr">
         <is>
@@ -7704,7 +7704,7 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>платежи по текущей деятельности - всего</t>
+          <t>платежи по инвестиционной деятельности - всего</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -7714,13 +7714,13 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>PlatPoTekDeVsego</t>
+          <t>PlPoInvDeyt</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="n">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B293" t="inlineStr">
         <is>
@@ -7729,7 +7729,7 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>платежи по инвестиционной деятельности - всего</t>
+          <t>платежи по финансовой деятельности – всего</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -7739,30 +7739,205 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>PlPoInvDeyt</t>
+          <t>PlPoFin</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="n">
+        <v>131</v>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>T24_000000_t29Ved14.xlsx</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>поступления по текущей деятельности - всего</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>всего</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>PostPoTekDeVsego</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="n">
+        <v>131</v>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>T24_000000_t29Ved14.xlsx</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>платежи по текущей деятельности - всего</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>всего</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>PlatPoTekDeVsego</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="n">
+        <v>131</v>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>T24_000000_t29Ved14.xlsx</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>платежи по инвестиционной деятельности - всего</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>всего</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>PlPoInvDeyt</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="n">
+        <v>131</v>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>T24_000000_t29Ved14.xlsx</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>платежи по финансовой деятельности – всего</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>всего</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>PlPoFin</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="n">
         <v>132</v>
       </c>
-      <c r="B294" t="inlineStr">
-        <is>
-          <t>T24_000000_t29Ved14.xlsx</t>
-        </is>
-      </c>
-      <c r="C294" t="inlineStr">
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>T24_000000_t29Ved14.xlsx</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>поступления по текущей деятельности - всего</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>всего</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>PostPoTekDeVsego</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="n">
+        <v>132</v>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>T24_000000_t29Ved14.xlsx</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>платежи по текущей деятельности - всего</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>всего</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>PlatPoTekDeVsego</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="n">
+        <v>132</v>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>T24_000000_t29Ved14.xlsx</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>платежи по инвестиционной деятельности - всего</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>всего</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>PlPoInvDeyt</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="n">
+        <v>132</v>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>T24_000000_t29Ved14.xlsx</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
         <is>
           <t>платежи по финансовой деятельности – всего</t>
         </is>
       </c>
-      <c r="D294" t="inlineStr">
-        <is>
-          <t>всего</t>
-        </is>
-      </c>
-      <c r="E294" t="inlineStr">
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>всего</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr">
         <is>
           <t>PlPoFin</t>
         </is>

--- a/output/совпадения_после_отбрасывания_префикса.xlsx
+++ b/output/совпадения_после_отбрасывания_префикса.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -445,526 +445,76 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>107</v>
+        <v>24</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>T24_000000_t29Ved14.xlsx</t>
+          <t>M25_000000_t03Ved14.xlsx</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>поступления по текущей деятельности прочие поступления</t>
+          <t>внеоборотные активы в том числе материальные внеоборотные активы(включая основные средства, незавершенные капитальные вложения в основные средства)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>прочие поступления</t>
+          <t>материальные внеоборотные активы включая основные средства незавершенные капитальные вложения в основные средства</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>PrTekDeVsego</t>
+          <t>VneAktVToChiMatVneAktOsnSreNezKapVloVOsnSre</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>108</v>
+        <v>24</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>T24_000000_t29Ved14.xlsx</t>
+          <t>M25_000000_t03Ved14.xlsx</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>поступления по текущей деятельности прочие поступления</t>
+          <t>внеоборотные активы в том числе нематериальные ,финансовые и другие внеоборотные активы</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>прочие поступления</t>
+          <t>нематериальные финансовые и другие внеоборотные активы</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>PrTekDeVsego</t>
+          <t>VneAktVToChiNem,fiIDruVneAkt</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>109</v>
+        <v>85</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>T24_000000_t29Ved14.xlsx</t>
+          <t>M25_000000_t25FsVed14.xlsx</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>поступления по текущей деятельности прочие поступления</t>
+          <t>организации, получившие прибыль в % к общему количеству</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>прочие поступления</t>
+          <t>в к общему количеству</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>PrTekDeVsego</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>110</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>T24_000000_t29Ved14.xlsx</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>поступления по текущей деятельности прочие поступления</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>прочие поступления</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>PrTekDeVsego</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>111</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>T24_000000_t29Ved14.xlsx</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>поступления по текущей деятельности прочие поступления</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>прочие поступления</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>PrTekDeVsego</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>112</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>T24_000000_t29Ved14.xlsx</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>поступления по текущей деятельности прочие поступления</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>прочие поступления</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>PrTekDeVsego</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>113</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>T24_000000_t29Ved14.xlsx</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>платежи по текущей деятельности прочие платежи</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>прочие платежи</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>ProchiePlatezhi</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>114</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>T24_000000_t29Ved14.xlsx</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>платежи по текущей деятельности прочие платежи</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>прочие платежи</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>ProchiePlatezhi</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>115</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>T24_000000_t29Ved14.xlsx</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>платежи по текущей деятельности прочие платежи</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>прочие платежи</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>ProchiePlatezhi</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>116</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>T24_000000_t29Ved14.xlsx</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>платежи по текущей деятельности прочие платежи</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>прочие платежи</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>ProchiePlatezhi</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>117</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>T24_000000_t29Ved14.xlsx</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>поступления денежных средств по инвестиционной деятельности прочие поступления</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>прочие поступления</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>PrPostDeyt</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>118</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>T24_000000_t29Ved14.xlsx</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>поступления денежных средств по инвестиционной деятельности прочие поступления</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>прочие поступления</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>PrPostDeyt</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>119</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>T24_000000_t29Ved14.xlsx</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>поступления денежных средств по инвестиционной деятельности прочие поступления</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>прочие поступления</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>PrPostDeyt</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>120</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>T24_000000_t29Ved14.xlsx</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>поступления денежных средств по инвестиционной деятельности прочие поступления</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>прочие поступления</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>PrPostDeyt</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>121</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>T24_000000_t29Ved14.xlsx</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>платежи по инвестиционной деятельности прочие платежи</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>прочие платежи</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>PrPl</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>122</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>T24_000000_t29Ved14.xlsx</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>платежи по инвестиционной деятельности прочие платежи</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>прочие платежи</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>PrPl</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>123</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>T24_000000_t29Ved14.xlsx</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>платежи по инвестиционной деятельности прочие платежи</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>прочие платежи</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>PrPl</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>124</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>T24_000000_t29Ved14.xlsx</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>платежи по инвестиционной деятельности прочие платежи</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>прочие платежи</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>PrPl</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>127</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>T24_000000_t29Ved14.xlsx</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>платежи по финансовой деятельности прочие платежи</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>прочие платежи</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>PrPoFin</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>128</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>T24_000000_t29Ved14.xlsx</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>платежи по финансовой деятельности прочие платежи</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>прочие платежи</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>PrPoFin</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>129</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>T24_000000_t29Ved14.xlsx</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>платежи по финансовой деятельности прочие платежи</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>прочие платежи</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>PrPoFin</t>
+          <t>OrgPolPriV%KObsKol_1</t>
         </is>
       </c>
     </row>

--- a/output/совпадения_после_отбрасывания_префикса.xlsx
+++ b/output/совпадения_после_отбрасывания_префикса.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -495,24 +495,224 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
+        <v>25</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>M25_000000_t03Ved14.xlsx</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>внеоборотные активы в том числе материальные внеоборотные активы(включая основные средства, незавершенные капитальные вложения в основные средства)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>материальные внеоборотные активы включая основные средства незавершенные капитальные вложения в основные средства</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>VneAktVToChiMatVneAktOsnSreNezKapVloVOsnSre</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>25</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>M25_000000_t03Ved14.xlsx</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>внеоборотные активы в том числе нематериальные ,финансовые и другие внеоборотные активы</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>нематериальные финансовые и другие внеоборотные активы</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>VneAktVToChiNem,fiIDruVneAkt</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>26</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>M25_000000_t03Ved14.xlsx</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>внеоборотные активы в том числе материальные внеоборотные активы(включая основные средства, незавершенные капитальные вложения в основные средства)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>материальные внеоборотные активы включая основные средства незавершенные капитальные вложения в основные средства</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>VneAktVToChiMatVneAktOsnSreNezKapVloVOsnSre</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>26</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>M25_000000_t03Ved14.xlsx</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>внеоборотные активы в том числе нематериальные ,финансовые и другие внеоборотные активы</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>нематериальные финансовые и другие внеоборотные активы</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>VneAktVToChiNem,fiIDruVneAkt</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>27</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>M25_000000_t03Ved14.xlsx</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>внеоборотные активы в том числе материальные внеоборотные активы(включая основные средства, незавершенные капитальные вложения в основные средства)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>материальные внеоборотные активы включая основные средства незавершенные капитальные вложения в основные средства</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>VneAktVToChiMatVneAktOsnSreNezKapVloVOsnSre</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>27</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>M25_000000_t03Ved14.xlsx</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>внеоборотные активы в том числе нематериальные ,финансовые и другие внеоборотные активы</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>нематериальные финансовые и другие внеоборотные активы</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>VneAktVToChiNem,fiIDruVneAkt</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>28</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>M25_000000_t03Ved14.xlsx</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>внеоборотные активы в том числе материальные внеоборотные активы(включая основные средства, незавершенные капитальные вложения в основные средства)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>материальные внеоборотные активы включая основные средства незавершенные капитальные вложения в основные средства</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>VneAktVToChiMatVneAktOsnSreNezKapVloVOsnSre</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>28</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>M25_000000_t03Ved14.xlsx</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>внеоборотные активы в том числе нематериальные ,финансовые и другие внеоборотные активы</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>нематериальные финансовые и другие внеоборотные активы</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>VneAktVToChiNem,fiIDruVneAkt</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
         <v>85</v>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>M25_000000_t25FsVed14.xlsx</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>организации, получившие прибыль в % к общему количеству</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>в к общему количеству</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>OrgPolPriV%KObsKol_1</t>
         </is>

--- a/output/совпадения_после_отбрасывания_префикса.xlsx
+++ b/output/совпадения_после_отбрасывания_префикса.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -743,6 +743,1756 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>93</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>S25_000000_t23-прVed14.xlsx</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>предыдущий год (сопоставимый круг) доходы и расходы по обычным видам деятельности выручка</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>доходы и расходы по обычным видам деятельности выручка</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>PreGo(soKruDohIRasPoObyVidDeyVyr</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>93</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>S25_000000_t23-прVed14.xlsx</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>предыдущий год (сопоставимый круг) доходы и расходы по обычным видам деятельности себестоимость с учетом коммерческих и управленческих расходов</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>себестоимость с учетом коммерческих и управленческих расходов</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>PreGo(soKruDohIRasPoObyVidDeySebSUchKomIUprRas</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>93</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>S25_000000_t23-прVed14.xlsx</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>предыдущий год (сопоставимый круг) доходы и расходы по обычным видам деятельности прибыль, убыток (-) от продаж</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>прибыль убыток от продаж</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>PreGo(soKruDohIRasPoObyVidDeyPriUby(-OtPro</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>93</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>S25_000000_t23-прVed14.xlsx</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>предыдущий год (сопоставимый круг) сальдо прочих доходов и расходов</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>сальдо прочих доходов и расходов</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>PreGo(soKruSalProDohIRas</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>93</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>S25_000000_t23-прVed14.xlsx</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>предыдущий год (сопоставимый круг) прибыль (убыток) от продолжающейся деятельности до налогообложения</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>прибыль убыток от продолжающейся деятельности до налогообложения</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>PreGo(soKruPri(ubOtProDeyDoNal</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>93</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>S25_000000_t23-прVed14.xlsx</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>предыдущий год (сопоставимый круг) налог на прибыль</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>налог на прибыль</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>PreGo(soKruNalNaPri</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>93</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>S25_000000_t23-прVed14.xlsx</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>предыдущий год (сопоставимый круг) чистая прибыль (убыток)</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>чистая прибыль убыток</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>PreGo(soKruChiPri(ub</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>94</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>S25_000000_t23-прVed14.xlsx</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>предыдущий год (сопоставимый круг) доходы и расходы по обычным видам деятельности выручка</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>доходы и расходы по обычным видам деятельности выручка</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>PreGo(soKruDohIRasPoObyVidDeyVyr</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>94</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>S25_000000_t23-прVed14.xlsx</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>предыдущий год (сопоставимый круг) доходы и расходы по обычным видам деятельности себестоимость с учетом коммерческих и управленческих расходов</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>себестоимость с учетом коммерческих и управленческих расходов</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>PreGo(soKruDohIRasPoObyVidDeySebSUchKomIUprRas</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>94</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>S25_000000_t23-прVed14.xlsx</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>предыдущий год (сопоставимый круг) доходы и расходы по обычным видам деятельности прибыль, убыток (-) от продаж</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>прибыль убыток от продаж</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>PreGo(soKruDohIRasPoObyVidDeyPriUby(-OtPro</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>94</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>S25_000000_t23-прVed14.xlsx</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>предыдущий год (сопоставимый круг) сальдо прочих доходов и расходов</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>сальдо прочих доходов и расходов</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>PreGo(soKruSalProDohIRas</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>94</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>S25_000000_t23-прVed14.xlsx</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>предыдущий год (сопоставимый круг) прибыль (убыток) от продолжающейся деятельности до налогообложения</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>прибыль убыток от продолжающейся деятельности до налогообложения</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>PreGo(soKruPri(ubOtProDeyDoNal</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>94</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>S25_000000_t23-прVed14.xlsx</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>предыдущий год (сопоставимый круг) налог на прибыль</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>налог на прибыль</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>PreGo(soKruNalNaPri</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>94</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>S25_000000_t23-прVed14.xlsx</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>предыдущий год (сопоставимый круг) чистая прибыль (убыток)</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>чистая прибыль убыток</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>PreGo(soKruChiPri(ub</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>95</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>S25_000000_t23-прVed14.xlsx</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>предыдущий год (сопоставимый круг) доходы и расходы по обычным видам деятельности выручка</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>доходы и расходы по обычным видам деятельности выручка</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>PreGo(soKruDohIRasPoObyVidDeyVyr</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>95</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>S25_000000_t23-прVed14.xlsx</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>предыдущий год (сопоставимый круг) доходы и расходы по обычным видам деятельности себестоимость с учетом коммерческих и управленческих расходов</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>себестоимость с учетом коммерческих и управленческих расходов</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>PreGo(soKruDohIRasPoObyVidDeySebSUchKomIUprRas</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>95</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>S25_000000_t23-прVed14.xlsx</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>предыдущий год (сопоставимый круг) доходы и расходы по обычным видам деятельности прибыль, убыток (-) от продаж</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>прибыль убыток от продаж</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>PreGo(soKruDohIRasPoObyVidDeyPriUby(-OtPro</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>95</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>S25_000000_t23-прVed14.xlsx</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>предыдущий год (сопоставимый круг) сальдо прочих доходов и расходов</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>сальдо прочих доходов и расходов</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>PreGo(soKruSalProDohIRas</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>95</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>S25_000000_t23-прVed14.xlsx</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>предыдущий год (сопоставимый круг) прибыль (убыток) от продолжающейся деятельности до налогообложения</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>прибыль убыток от продолжающейся деятельности до налогообложения</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>PreGo(soKruPri(ubOtProDeyDoNal</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>95</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>S25_000000_t23-прVed14.xlsx</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>предыдущий год (сопоставимый круг) налог на прибыль</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>налог на прибыль</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>PreGo(soKruNalNaPri</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>95</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>S25_000000_t23-прVed14.xlsx</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>предыдущий год (сопоставимый круг) чистая прибыль (убыток)</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>чистая прибыль убыток</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>PreGo(soKruChiPri(ub</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>96</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>S25_000000_t23-прVed14.xlsx</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>предыдущий год (сопоставимый круг) доходы и расходы по обычным видам деятельности выручка</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>доходы и расходы по обычным видам деятельности выручка</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>PreGo(soKruDohIRasPoObyVidDeyVyr</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>96</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>S25_000000_t23-прVed14.xlsx</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>предыдущий год (сопоставимый круг) доходы и расходы по обычным видам деятельности себестоимость с учетом коммерческих и управленческих расходов</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>себестоимость с учетом коммерческих и управленческих расходов</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>PreGo(soKruDohIRasPoObyVidDeySebSUchKomIUprRas</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>96</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>S25_000000_t23-прVed14.xlsx</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>предыдущий год (сопоставимый круг) доходы и расходы по обычным видам деятельности прибыль, убыток (-) от продаж</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>прибыль убыток от продаж</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>PreGo(soKruDohIRasPoObyVidDeyPriUby(-OtPro</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>96</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>S25_000000_t23-прVed14.xlsx</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>предыдущий год (сопоставимый круг) сальдо прочих доходов и расходов</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>сальдо прочих доходов и расходов</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>PreGo(soKruSalProDohIRas</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>96</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>S25_000000_t23-прVed14.xlsx</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>предыдущий год (сопоставимый круг) прибыль (убыток) от продолжающейся деятельности до налогообложения</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>прибыль убыток от продолжающейся деятельности до налогообложения</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>PreGo(soKruPri(ubOtProDeyDoNal</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>96</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>S25_000000_t23-прVed14.xlsx</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>предыдущий год (сопоставимый круг) налог на прибыль</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>налог на прибыль</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>PreGo(soKruNalNaPri</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>96</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>S25_000000_t23-прVed14.xlsx</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>предыдущий год (сопоставимый круг) чистая прибыль (убыток)</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>чистая прибыль убыток</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>PreGo(soKruChiPri(ub</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>97</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>S25_000000_t23-прVed14.xlsx</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>предыдущий год (сопоставимый круг) доходы и расходы по обычным видам деятельности выручка</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>доходы и расходы по обычным видам деятельности выручка</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>PreGo(soKruDohIRasPoObyVidDeyVyr</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>97</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>S25_000000_t23-прVed14.xlsx</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>предыдущий год (сопоставимый круг) доходы и расходы по обычным видам деятельности себестоимость с учетом коммерческих и управленческих расходов</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>себестоимость с учетом коммерческих и управленческих расходов</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>PreGo(soKruDohIRasPoObyVidDeySebSUchKomIUprRas</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>97</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>S25_000000_t23-прVed14.xlsx</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>предыдущий год (сопоставимый круг) доходы и расходы по обычным видам деятельности прибыль, убыток (-) от продаж</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>прибыль убыток от продаж</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>PreGo(soKruDohIRasPoObyVidDeyPriUby(-OtPro</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>97</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>S25_000000_t23-прVed14.xlsx</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>предыдущий год (сопоставимый круг) сальдо прочих доходов и расходов</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>сальдо прочих доходов и расходов</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>PreGo(soKruSalProDohIRas</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>97</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>S25_000000_t23-прVed14.xlsx</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>предыдущий год (сопоставимый круг) прибыль (убыток) от продолжающейся деятельности до налогообложения</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>прибыль убыток от продолжающейся деятельности до налогообложения</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>PreGo(soKruPri(ubOtProDeyDoNal</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>97</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>S25_000000_t23-прVed14.xlsx</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>предыдущий год (сопоставимый круг) налог на прибыль</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>налог на прибыль</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>PreGo(soKruNalNaPri</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>97</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>S25_000000_t23-прVed14.xlsx</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>предыдущий год (сопоставимый круг) чистая прибыль (убыток)</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>чистая прибыль убыток</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>PreGo(soKruChiPri(ub</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>98</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>S25_000000_t23-прVed14.xlsx</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>предыдущий год (сопоставимый круг) доходы и расходы по обычным видам деятельности выручка</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>доходы и расходы по обычным видам деятельности выручка</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>PreGo(soKruDohIRasPoObyVidDeyVyr</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>98</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>S25_000000_t23-прVed14.xlsx</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>предыдущий год (сопоставимый круг) доходы и расходы по обычным видам деятельности себестоимость с учетом коммерческих и управленческих расходов</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>себестоимость с учетом коммерческих и управленческих расходов</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>PreGo(soKruDohIRasPoObyVidDeySebSUchKomIUprRas</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>98</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>S25_000000_t23-прVed14.xlsx</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>предыдущий год (сопоставимый круг) доходы и расходы по обычным видам деятельности прибыль, убыток (-) от продаж</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>прибыль убыток от продаж</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>PreGo(soKruDohIRasPoObyVidDeyPriUby(-OtPro</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>98</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>S25_000000_t23-прVed14.xlsx</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>предыдущий год (сопоставимый круг) сальдо прочих доходов и расходов</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>сальдо прочих доходов и расходов</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>PreGo(soKruSalProDohIRas</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>98</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>S25_000000_t23-прVed14.xlsx</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>предыдущий год (сопоставимый круг) прибыль (убыток) от продолжающейся деятельности до налогообложения</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>прибыль убыток от продолжающейся деятельности до налогообложения</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>PreGo(soKruPri(ubOtProDeyDoNal</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>98</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>S25_000000_t23-прVed14.xlsx</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>предыдущий год (сопоставимый круг) налог на прибыль</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>налог на прибыль</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>PreGo(soKruNalNaPri</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>98</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>S25_000000_t23-прVed14.xlsx</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>предыдущий год (сопоставимый круг) чистая прибыль (убыток)</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>чистая прибыль убыток</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>PreGo(soKruChiPri(ub</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>99</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>S25_000000_t23-прVed14.xlsx</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>предыдущий год (сопоставимый круг) доходы и расходы по обычным видам деятельности выручка</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>доходы и расходы по обычным видам деятельности выручка</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>PreGo(soKruDohIRasPoObyVidDeyVyr</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>99</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>S25_000000_t23-прVed14.xlsx</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>предыдущий год (сопоставимый круг) доходы и расходы по обычным видам деятельности себестоимость с учетом коммерческих и управленческих расходов</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>себестоимость с учетом коммерческих и управленческих расходов</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>PreGo(soKruDohIRasPoObyVidDeySebSUchKomIUprRas</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>99</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>S25_000000_t23-прVed14.xlsx</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>предыдущий год (сопоставимый круг) доходы и расходы по обычным видам деятельности прибыль, убыток (-) от продаж</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>прибыль убыток от продаж</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>PreGo(soKruDohIRasPoObyVidDeyPriUby(-OtPro</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>99</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>S25_000000_t23-прVed14.xlsx</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>предыдущий год (сопоставимый круг) сальдо прочих доходов и расходов</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>сальдо прочих доходов и расходов</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>PreGo(soKruSalProDohIRas</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>99</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>S25_000000_t23-прVed14.xlsx</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>предыдущий год (сопоставимый круг) прибыль (убыток) от продолжающейся деятельности до налогообложения</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>прибыль убыток от продолжающейся деятельности до налогообложения</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>PreGo(soKruPri(ubOtProDeyDoNal</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>99</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>S25_000000_t23-прVed14.xlsx</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>предыдущий год (сопоставимый круг) налог на прибыль</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>налог на прибыль</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>PreGo(soKruNalNaPri</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>99</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>S25_000000_t23-прVed14.xlsx</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>предыдущий год (сопоставимый круг) чистая прибыль (убыток)</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>чистая прибыль убыток</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>PreGo(soKruChiPri(ub</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>100</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>S25_000000_t23-прVed14.xlsx</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>предыдущий год (сопоставимый круг) доходы и расходы по обычным видам деятельности выручка</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>доходы и расходы по обычным видам деятельности выручка</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>PreGo(soKruDohIRasPoObyVidDeyVyr</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>100</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>S25_000000_t23-прVed14.xlsx</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>предыдущий год (сопоставимый круг) доходы и расходы по обычным видам деятельности себестоимость с учетом коммерческих и управленческих расходов</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>себестоимость с учетом коммерческих и управленческих расходов</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>PreGo(soKruDohIRasPoObyVidDeySebSUchKomIUprRas</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>100</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>S25_000000_t23-прVed14.xlsx</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>предыдущий год (сопоставимый круг) доходы и расходы по обычным видам деятельности прибыль, убыток (-) от продаж</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>прибыль убыток от продаж</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>PreGo(soKruDohIRasPoObyVidDeyPriUby(-OtPro</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>100</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>S25_000000_t23-прVed14.xlsx</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>предыдущий год (сопоставимый круг) сальдо прочих доходов и расходов</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>сальдо прочих доходов и расходов</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>PreGo(soKruSalProDohIRas</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>100</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>S25_000000_t23-прVed14.xlsx</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>предыдущий год (сопоставимый круг) прибыль (убыток) от продолжающейся деятельности до налогообложения</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>прибыль убыток от продолжающейся деятельности до налогообложения</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>PreGo(soKruPri(ubOtProDeyDoNal</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>100</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>S25_000000_t23-прVed14.xlsx</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>предыдущий год (сопоставимый круг) налог на прибыль</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>налог на прибыль</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>PreGo(soKruNalNaPri</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>100</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>S25_000000_t23-прVed14.xlsx</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>предыдущий год (сопоставимый круг) чистая прибыль (убыток)</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>чистая прибыль убыток</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>PreGo(soKruChiPri(ub</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>101</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>S25_000000_t23-прVed14.xlsx</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>предыдущий год (сопоставимый круг) доходы и расходы по обычным видам деятельности выручка</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>доходы и расходы по обычным видам деятельности выручка</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>PreGo(soKruDohIRasPoObyVidDeyVyr</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>101</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>S25_000000_t23-прVed14.xlsx</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>предыдущий год (сопоставимый круг) доходы и расходы по обычным видам деятельности себестоимость с учетом коммерческих и управленческих расходов</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>себестоимость с учетом коммерческих и управленческих расходов</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>PreGo(soKruDohIRasPoObyVidDeySebSUchKomIUprRas</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>101</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>S25_000000_t23-прVed14.xlsx</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>предыдущий год (сопоставимый круг) доходы и расходы по обычным видам деятельности прибыль, убыток (-) от продаж</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>прибыль убыток от продаж</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>PreGo(soKruDohIRasPoObyVidDeyPriUby(-OtPro</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>101</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>S25_000000_t23-прVed14.xlsx</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>предыдущий год (сопоставимый круг) сальдо прочих доходов и расходов</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>сальдо прочих доходов и расходов</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>PreGo(soKruSalProDohIRas</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>101</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>S25_000000_t23-прVed14.xlsx</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>предыдущий год (сопоставимый круг) прибыль (убыток) от продолжающейся деятельности до налогообложения</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>прибыль убыток от продолжающейся деятельности до налогообложения</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>PreGo(soKruPri(ubOtProDeyDoNal</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>101</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>S25_000000_t23-прVed14.xlsx</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>предыдущий год (сопоставимый круг) налог на прибыль</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>налог на прибыль</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>PreGo(soKruNalNaPri</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>101</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>S25_000000_t23-прVed14.xlsx</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>предыдущий год (сопоставимый круг) чистая прибыль (убыток)</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>чистая прибыль убыток</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>PreGo(soKruChiPri(ub</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>102</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>S25_000000_t23-прVed14.xlsx</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>предыдущий год (сопоставимый круг) доходы и расходы по обычным видам деятельности выручка</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>доходы и расходы по обычным видам деятельности выручка</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>PreGo(soKruDohIRasPoObyVidDeyVyr</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>102</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>S25_000000_t23-прVed14.xlsx</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>предыдущий год (сопоставимый круг) доходы и расходы по обычным видам деятельности себестоимость с учетом коммерческих и управленческих расходов</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>себестоимость с учетом коммерческих и управленческих расходов</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>PreGo(soKruDohIRasPoObyVidDeySebSUchKomIUprRas</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>102</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>S25_000000_t23-прVed14.xlsx</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>предыдущий год (сопоставимый круг) доходы и расходы по обычным видам деятельности прибыль, убыток (-) от продаж</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>прибыль убыток от продаж</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>PreGo(soKruDohIRasPoObyVidDeyPriUby(-OtPro</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>102</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>S25_000000_t23-прVed14.xlsx</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>предыдущий год (сопоставимый круг) сальдо прочих доходов и расходов</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>сальдо прочих доходов и расходов</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>PreGo(soKruSalProDohIRas</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>102</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>S25_000000_t23-прVed14.xlsx</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>предыдущий год (сопоставимый круг) прибыль (убыток) от продолжающейся деятельности до налогообложения</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>прибыль убыток от продолжающейся деятельности до налогообложения</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>PreGo(soKruPri(ubOtProDeyDoNal</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>102</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>S25_000000_t23-прVed14.xlsx</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>предыдущий год (сопоставимый круг) налог на прибыль</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>налог на прибыль</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>PreGo(soKruNalNaPri</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>102</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>S25_000000_t23-прVed14.xlsx</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>предыдущий год (сопоставимый круг) чистая прибыль (убыток)</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>чистая прибыль убыток</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>PreGo(soKruChiPri(ub</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
